--- a/naver-place-crawler/results_nail/연제구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/연제구_네일샵.xlsx
@@ -417,16 +417,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V119"/>
+  <dimension ref="A1:V121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="47" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,25 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>하정수네일</t>
+          <t>바비랑네일</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0hyeah6@naver.com</t>
+          <t>rladbrud8791@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>051-867-9910</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 종합운동장로12번길 34</t>
+          <t>부산광역시 연제구 중앙대로1039번길 15 . 1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>http://instagram.com/hjsnail</t>
+          <t>https://www.instagram.com/babirang_</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -617,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R2" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -632,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1060527554</t>
+          <t>950132087</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060527554</t>
+          <t>https://m.place.naver.com/place/950132087</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -654,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>엔피케어 부산연산점</t>
+          <t>모모네일</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>np_care@naver.com</t>
+          <t>brenda70@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1449-2096</t>
+          <t>0507-1334-5238</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1114 4층</t>
+          <t>부산광역시 연제구 명륜로2번길 32 3층 모모네일</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NPCARE_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -686,12 +690,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -707,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>578</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>715</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -726,17 +730,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1204729944</t>
+          <t>1664773879</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1204729944</t>
+          <t>https://m.place.naver.com/place/1664773879</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -748,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>네일바</t>
+          <t>더네일</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rosamatt@naver.com</t>
+          <t>thenail_@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>051-758-3963</t>
+          <t>0507-1311-1145</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 80 1층</t>
+          <t>부산광역시 연제구 거제대로178번길 55-1 더네일</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_bar._</t>
+          <t>http://www.instagram.com/the_nail120</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="n">
-        <v>64</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,17 +824,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>32333430</t>
+          <t>1230694056</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32333430</t>
+          <t>https://m.place.naver.com/place/1230694056</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -842,29 +846,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>네일커밍</t>
+          <t>뷰티빛담</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>coming230201@naver.com</t>
+          <t>dksdudtjs1234@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1327-0497</t>
+          <t>0507-1337-6219</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로208번길 16</t>
+          <t>부산광역시 연제구 중앙천로 7 104호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/coming230201</t>
+          <t>https://instagram.com/beauty_bitdam?utm_medium=copy_link</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -879,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -899,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>160</v>
+        <v>553</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="R5" t="n">
-        <v>184</v>
+        <v>561</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -914,17 +918,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1185455703</t>
+          <t>1482685574</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185455703</t>
+          <t>https://m.place.naver.com/place/1482685574</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -936,29 +940,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>연산동_네일,더빛날</t>
+          <t>유화네일 부산시청점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>potato00214@naver.com</t>
+          <t>zkscy711@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1432-1799</t>
+          <t>0507-1427-6564</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1076번길 30 1층</t>
+          <t>부산광역시 연제구 중앙천로 81-17 1층 102호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_thevitnal</t>
+          <t>https://www.instagram.com/yuhwa__nail</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -993,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="Q6" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>154</v>
+        <v>37</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,17 +1012,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1424947348</t>
+          <t>1340666587</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1424947348</t>
+          <t>https://m.place.naver.com/place/1340666587</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1030,34 +1034,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>오드레 네일</t>
+          <t>하루네일</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>seunjeung@naver.com</t>
+          <t>luv744@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1436-2772</t>
+          <t>051-868-7333</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로22번길 36 401동 103일부호</t>
+          <t>부산광역시 연제구 거제천로255번가길 31 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/odrenail</t>
+          <t>https://booking.naver.com/booking/13/bizes/526220</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1078,7 +1082,7 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1087,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="R7" t="n">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1326125631</t>
+          <t>1884949089</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1326125631</t>
+          <t>https://m.place.naver.com/place/1884949089</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1124,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2월11일네일</t>
+          <t>투에이치 뷰티</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>211nail_0211@naver.com</t>
+          <t>jieun961216@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1329-6882</t>
+          <t>0507-1391-0868</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1063 5층</t>
+          <t>부산광역시 연제구 신촌로 2 5층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/211_nail</t>
+          <t>https://open.kakao.com/o/sZa5dynf</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1172,7 +1176,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1181,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>211</v>
+        <v>67</v>
       </c>
       <c r="Q8" t="n">
         <v>58</v>
       </c>
       <c r="R8" t="n">
-        <v>269</v>
+        <v>125</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,17 +1200,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1816506274</t>
+          <t>1263305975</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816506274</t>
+          <t>https://m.place.naver.com/place/1263305975</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1218,25 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>여우네일</t>
+          <t>엘유네일</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>assajuju1104@naver.com</t>
+          <t>kikanaa@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1306-9767</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로 82 2층</t>
+          <t>부산광역시 연제구 중앙대로1075번길 58 1층 엘유네일</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/lu_nail___</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1246,7 +1254,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1267,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>19997542</t>
+          <t>2036505455</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19997542</t>
+          <t>https://m.place.naver.com/place/2036505455</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1308,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>네일오예</t>
+          <t>연산동_네일,더빛날</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>efjekkk0888@naver.com</t>
+          <t>potato00214@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1424-0360</t>
+          <t>0507-1432-1799</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 해맞이로67번길 23 102호</t>
+          <t>부산광역시 연제구 중앙대로1076번길 30 1층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_o.yeah?igsh=MTBrcDN2OHM5djY1cQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail_thevitnal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1365,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,17 +1388,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2070499527</t>
+          <t>1424947348</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2070499527</t>
+          <t>https://m.place.naver.com/place/1424947348</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1402,34 +1410,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>뷰티진담</t>
+          <t>네일존 이마트연제점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>daily_luhee@naver.com</t>
+          <t>nailzone__@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1321-5412</t>
+          <t>0507-1448-9396</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1043번길 34 시청역 sk뷰 2층 206호</t>
+          <t>부산광역시 연제구 연수로 89 이마트 연제점 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>http://open.kakao.com/me/beauty_jindam</t>
+          <t>https://blog.naver.com/nailzone__</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1439,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1450,7 +1458,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1459,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>42</v>
+        <v>221</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="R11" t="n">
-        <v>60</v>
+        <v>255</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1992381741</t>
+          <t>1531070526</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1992381741</t>
+          <t>https://m.place.naver.com/place/1531070526</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1496,29 +1504,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>더혜뷰티 연산양정점</t>
+          <t>핑크네일</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>zlwm4@naver.com</t>
+          <t>kwy765300@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1471-0417</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로87번길 3 3층</t>
+          <t>부산광역시 연제구 쌍미천로 120 핑크네일</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>http://instagram.com/the_hye_beauty</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1528,7 +1532,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1549,17 +1553,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>484</v>
+        <v>16</v>
       </c>
       <c r="Q12" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="R12" t="n">
-        <v>509</v>
+        <v>119</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,17 +1572,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1695025021</t>
+          <t>1040392199</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695025021</t>
+          <t>https://m.place.naver.com/place/1040392199</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1590,29 +1594,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네시일분 예뻐지는시간</t>
+          <t>네일예쁨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>alal7667@naver.com</t>
+          <t>maeilyepboom@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1335-9404</t>
+          <t>0507-1463-5608</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로343번길 22 더스타a동 101호 네시일분</t>
+          <t>부산광역시 연제구 연제로 21 힐스테이트상가 2층 203호(홍익노무법인건물)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nesiilbun_beauty</t>
+          <t>https://www.instagram.com/adst8888</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1647,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="R13" t="n">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1666,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1660019694</t>
+          <t>1462213612</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1660019694</t>
+          <t>https://m.place.naver.com/place/1462213612</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1688,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ONE네일</t>
+          <t>네일다다</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>garam_soo@naver.com</t>
+          <t>kssstb539@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1349-6159</t>
+          <t>0507-1365-0495</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1049 3층</t>
+          <t>부산광역시 연제구 시청로 12 상가동 1층 113호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://instagram.com/onenail_onenail?igshid=ZDdkNTZiNTM=</t>
+          <t>https://www.instagram.com/nail_dada__</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1741,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>100</v>
+        <v>201</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>103</v>
+        <v>205</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,17 +1760,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1153323846</t>
+          <t>1083006557</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153323846</t>
+          <t>https://m.place.naver.com/place/1083006557</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1778,29 +1782,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>올바른 네일&amp;브로우</t>
+          <t>여우네일</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>stylemusee@naver.com</t>
+          <t>assajuju1104@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1416-7885</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 82 205호</t>
+          <t>부산광역시 연제구 아시아드대로 82 2층</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ab_browlab</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1831,17 +1831,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>213</v>
+        <v>1</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1850,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1021114766</t>
+          <t>19997542</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1021114766</t>
+          <t>https://m.place.naver.com/place/19997542</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1872,29 +1872,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>제이제이네일&amp;붙임머리 거제사직점</t>
+          <t>로제이네일</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>kiss121127@naver.com</t>
+          <t>permisi@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1335-5968</t>
+          <t>0507-1340-1354</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로 39 레이카운티 1단지상가 109호</t>
+          <t>부산광역시 연제구 과정로191번다길 61 로제이 네일</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jj__nail</t>
+          <t>https://www.instagram.com/ro.j_nail?igsh=MWU4ZXBiczVvaTdlaQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>384</v>
+        <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>416</v>
+        <v>1</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1944,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1823710447</t>
+          <t>1088938826</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1823710447</t>
+          <t>https://m.place.naver.com/place/1088938826</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1966,34 +1966,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일리크</t>
+          <t>네일요정</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nailique25@naver.com</t>
+          <t>duddnd121@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1449-2433</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로79번길 50 1층</t>
+          <t>부산광역시 연제구 안연로 8 1층 미앤끼헤어네일</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Vyesn</t>
+          <t>https://smartstore.naver.com/giggle_nailtip</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2014,7 +2010,7 @@
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2023,13 +2019,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>314</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>343</v>
+        <v>6</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,17 +2034,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1290184827</t>
+          <t>1208223075</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290184827</t>
+          <t>https://m.place.naver.com/place/1208223075</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2060,39 +2056,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>라온네일</t>
+          <t>효리의빛나는네일</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sungunara226@naver.com</t>
+          <t>too1823@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1364-1656</t>
+          <t>0507-1341-9746</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로32번길 23 1층</t>
+          <t>부산광역시 연제구 거제대로 275 상가동 지1층 107호</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>http://instagram.com/la_on_nail</t>
+          <t>https://toss.place/_lb/TZUW7eqR3</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2108,7 +2104,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2117,13 +2113,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="Q18" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="R18" t="n">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,17 +2128,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1100502822</t>
+          <t>2040725905</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1100502822</t>
+          <t>https://m.place.naver.com/place/2040725905</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2154,25 +2150,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>챠밍네일 연산점</t>
+          <t>마틸다네일</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ghdrldbwjd1@naver.com</t>
+          <t>wngml2572@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1363-7291</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로260번길 32 챠밍네일</t>
+          <t>부산광역시 연제구 신금로 18 2층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ghdrldbwjd1</t>
+          <t>https://open.kakao.com/o/stWnFTNg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2198,7 +2198,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2207,13 +2207,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>133</v>
+        <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="R19" t="n">
-        <v>152</v>
+        <v>42</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2222,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1458074178</t>
+          <t>1247183274</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1458074178</t>
+          <t>https://m.place.naver.com/place/1247183274</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2244,34 +2244,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>소르베네일 부산시청점</t>
+          <t>네일,도하</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>oladeoro@naver.com</t>
+          <t>nsj610@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1487-4679</t>
+          <t>0507-1498-5458</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1038번길 40 근린생활시설 D동 2층 208호</t>
+          <t>부산광역시 연제구 연수로11번길 114 1층 102호 네일,도하</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xdHhHn</t>
+          <t>https://www.instagram.com/nail_doha_</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2292,7 +2292,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="Q20" t="n">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2316,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2032602450</t>
+          <t>1673520422</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032602450</t>
+          <t>https://m.place.naver.com/place/1673520422</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2338,29 +2338,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>더미뉴네일</t>
+          <t>Nail빛</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mj_2023@naver.com</t>
+          <t>theshiny_nail@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1460-0699</t>
+          <t>0507-1322-9781</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 173 1층</t>
+          <t>부산광역시 연제구 반송로 80 연산동일동미라주 106동 1층상가 네일빛</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/theminew.nail</t>
+          <t>http://instagram.com/nail_ybit</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2395,13 +2395,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>129</v>
+        <v>300</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="R21" t="n">
-        <v>134</v>
+        <v>328</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,17 +2410,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1260374485</t>
+          <t>1478119147</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260374485</t>
+          <t>https://m.place.naver.com/place/1478119147</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2432,29 +2432,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>네일다다</t>
+          <t>코코로네일</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kssstb539@naver.com</t>
+          <t>romina97@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1365-0495</t>
+          <t>0507-1316-7319</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 시청로 12 상가동 1층 113호</t>
+          <t>부산광역시 연제구 과정로114번길 4 1층 코코로네일</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_dada__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2485,17 +2485,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>201</v>
+        <v>63</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>205</v>
+        <v>63</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2504,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1083006557</t>
+          <t>1258381982</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1083006557</t>
+          <t>https://m.place.naver.com/place/1258381982</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2526,29 +2526,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>이퓨리네일 연산점</t>
+          <t>오늘의네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ifurynail@naver.com</t>
+          <t>redcherry88@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1356-4466</t>
+          <t>0507-1398-3444</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로230번길 81 유성헤네스타워 상가 1층 이퓨리네일</t>
+          <t>부산광역시 연제구 고분로 254 1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ifurynail</t>
+          <t>http://instagram.com/cny3444</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2583,13 +2583,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>249</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="R23" t="n">
-        <v>284</v>
+        <v>32</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2598,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1044877447</t>
+          <t>1838257805</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044877447</t>
+          <t>https://m.place.naver.com/place/1838257805</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2620,25 +2620,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>꼭대기네일</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>벨라티뷰티 부산시청점</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>mijooaa@naver.com</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0507-1340-4140</t>
+          <t>0507-1477-0829</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 화지로 95 거제청구하이츠아파트 상가동 1층</t>
+          <t>부산광역시 연제구 신촌로 20 2층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/vellati_b?igsh=MWQ2NXlvN2J0Zmw2NQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2648,7 +2652,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2669,17 +2673,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R24" t="n">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2688,17 +2692,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1056754569</t>
+          <t>2002445034</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1056754569</t>
+          <t>https://m.place.naver.com/place/2002445034</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2710,29 +2714,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>영네일</t>
+          <t>네일르누보</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cy2403@naver.com</t>
+          <t>ekgus618@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>051-504-0506</t>
+          <t>0507-1459-8386</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로 95</t>
+          <t>부산광역시 연제구 아시아드대로 7 132동 204호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_renouveau_2?igsh=MW55NjlxOTE3dGUyaw==</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2742,7 +2746,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2763,17 +2767,17 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="Q25" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="R25" t="n">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,17 +2786,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1168856867</t>
+          <t>1342130355</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1168856867</t>
+          <t>https://m.place.naver.com/place/1342130355</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2804,25 +2808,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>투에이치 뷰티</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>더킴스네일뷰티</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>rlawlgo85@naver.com</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1391-0868</t>
+          <t>0507-1420-5259</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신촌로 2 5층</t>
+          <t>부산광역시 연제구 반송로 19 신종빌딩 5층</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sZa5dynf</t>
+          <t>https://www.instagram.com/thekims2012?igsh=Nmp3ZWN4NmRrYjA5&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2848,7 +2856,7 @@
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2857,13 +2865,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>67</v>
+        <v>232</v>
       </c>
       <c r="Q26" t="n">
-        <v>58</v>
+        <v>958</v>
       </c>
       <c r="R26" t="n">
-        <v>125</v>
+        <v>1190</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2872,17 +2880,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1263305975</t>
+          <t>31098912</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1263305975</t>
+          <t>https://m.place.naver.com/place/31098912</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2894,25 +2902,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>네일 더 예쁜</t>
+          <t>라움네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>dc2452@naver.com</t>
+          <t>realbarbie77@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0507-1445-8116</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로218번길 2 2층</t>
+          <t>부산광역시 연제구 월드컵대로73번길 4 1층 라움네일</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_raum__nail?igsh=MThxa3BoYmF1cGR0YQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2922,7 +2934,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2943,17 +2955,17 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2962,17 +2974,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>2054952880</t>
+          <t>1012943186</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2054952880</t>
+          <t>https://m.place.naver.com/place/1012943186</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -2984,12 +2996,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>바이요니네일</t>
+          <t>네일 더 예쁜</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>kitty_log@naver.com</t>
+          <t>dc2452@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2997,12 +3009,12 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로 77-2 1층</t>
+          <t>부산광역시 연제구 연수로218번길 2 2층</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://instagram.com/byyoni__nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3012,7 +3024,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3033,17 +3045,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>458</v>
+        <v>57</v>
       </c>
       <c r="Q28" t="n">
         <v>7</v>
       </c>
       <c r="R28" t="n">
-        <v>465</v>
+        <v>64</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3052,17 +3064,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>1418772825</t>
+          <t>2054952880</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418772825</t>
+          <t>https://m.place.naver.com/place/2054952880</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3074,29 +3086,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>로제이네일</t>
+          <t>유니스네일뷰티</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>permisi@naver.com</t>
+          <t>soyun4241@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1340-1354</t>
+          <t>0507-1382-4241</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로191번다길 61 로제이 네일</t>
+          <t>부산광역시 연제구 거제천로230번길 61 1층 유니스네일뷰티</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ro.j_nail?igsh=MWU4ZXBiczVvaTdlaQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/artist_yunice</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3131,13 +3143,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>167</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3146,17 +3158,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1088938826</t>
+          <t>1725318910</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088938826</t>
+          <t>https://m.place.naver.com/place/1725318910</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3168,25 +3180,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>벨루아뷰티</t>
+          <t>썬즈네일</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sh26888@naver.com</t>
+          <t>suns-nail@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1468-2628</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 쌍미천로 147 3층</t>
+          <t>부산광역시 연제구 아시아드대로28번길 9 상가동 1층 209호 썬즈네일</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bellua_beauty?igsh=MWltZ2hrbWZpYzAxdw%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/sunsnail</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3221,13 +3237,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="Q30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="R30" t="n">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3236,17 +3252,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2086054910</t>
+          <t>1468663766</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086054910</t>
+          <t>https://m.place.naver.com/place/1468663766</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3258,29 +3274,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>바나다네일</t>
+          <t>루미가넷 네일존 사직</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ksn0706@naver.com</t>
+          <t>webmore@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1332-8909</t>
+          <t>070-7012-9336</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 쌍미천로 163-1 바나다네일</t>
+          <t>부산광역시 연제구 종합운동장로 7 아시아드 홈플러스 지하1층 네일존</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ksn0706</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3290,12 +3306,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3311,17 +3327,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>129</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>162</v>
+        <v>3</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3330,17 +3346,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>34818659</t>
+          <t>1179495995</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34818659</t>
+          <t>https://m.place.naver.com/place/1179495995</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3352,25 +3368,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>핑크네일</t>
+          <t>페브네일</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>kwy765300@naver.com</t>
+          <t>yearning1128@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0507-1375-8044</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 쌍미천로 120 핑크네일</t>
+          <t>부산광역시 연제구 반송로 62-17 1층 페브네일</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/feb_nail</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3380,7 +3400,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3401,17 +3421,17 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>16</v>
+        <v>230</v>
       </c>
       <c r="Q32" t="n">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="R32" t="n">
-        <v>119</v>
+        <v>242</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3420,17 +3440,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1040392199</t>
+          <t>1968946087</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040392199</t>
+          <t>https://m.place.naver.com/place/1968946087</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3442,34 +3462,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>에스네일</t>
+          <t>네일블리진</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>7gonggu@naver.com</t>
+          <t>rkmgl2622@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0507-1303-4143</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 258 연산해수피아 1층 105호</t>
+          <t>부산광역시 연제구 중앙대로 1039-1 3층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/7gonggu</t>
+          <t>http://pf.kakao.com/_YxbxmQT</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3479,7 +3495,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3490,7 +3506,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3499,13 +3515,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="R33" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3514,17 +3530,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1772096643</t>
+          <t>1051433565</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1772096643</t>
+          <t>https://m.place.naver.com/place/1051433565</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3536,25 +3552,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>오브네일</t>
+          <t>명월네일샵</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ofrang@naver.com</t>
+          <t>leekatanail@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1461-1196</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로4번길 5 1층 102호</t>
+          <t>부산광역시 연제구 거제천로 246</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ove.nail?igsh=aWdkcjE3bDZiaHFi</t>
+          <t>https://blog.naver.com/leekatanail</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3569,7 +3589,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3589,13 +3609,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R34" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3604,17 +3624,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1870621262</t>
+          <t>1031904006</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870621262</t>
+          <t>https://m.place.naver.com/place/1031904006</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3626,34 +3646,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>럭스네일팁</t>
+          <t>뷰티진담</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>nailluxe@naver.com</t>
+          <t>daily_luhee@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1432-0046</t>
+          <t>0507-1321-5412</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제시장로 23</t>
+          <t>부산광역시 연제구 중앙대로1043번길 34 시청역 sk뷰 2층 206호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://www.luxenailtip.co.kr/</t>
+          <t>http://open.kakao.com/me/beauty_jindam</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3674,22 +3694,22 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3698,17 +3718,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>57487992</t>
+          <t>1992381741</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/57487992</t>
+          <t>https://m.place.naver.com/place/1992381741</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3720,29 +3740,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>딴네일</t>
+          <t>히니네일 부산연산점</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nobleliz_@naver.com</t>
+          <t>yuu_ja@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1413-7542</t>
+          <t>0507-1391-1454</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1134번길 51 1층 딴네일</t>
+          <t>부산광역시 연제구 중앙대로 1130 연산동 SK VIE W 2단지 1층 114호</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>http://instagram.com/ddan_nail7542</t>
+          <t>https://www.instagram.com/heeni_nail</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3777,13 +3797,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>27</v>
+        <v>112</v>
       </c>
       <c r="Q36" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="R36" t="n">
-        <v>30</v>
+        <v>136</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3792,17 +3812,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1750949440</t>
+          <t>1114751434</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1750949440</t>
+          <t>https://m.place.naver.com/place/1114751434</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3814,29 +3834,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>온 네일</t>
+          <t>럭스네일팁</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>guswnwnwn@naver.com</t>
+          <t>nailluxe@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1446-3360</t>
+          <t>0507-1432-0046</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 시청로 12 더샵씨티애비뉴2차 상가 2층215호</t>
+          <t>부산광역시 연제구 거제시장로 23</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.luxenailtip.co.kr/</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3846,7 +3866,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3871,13 +3891,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3886,17 +3906,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>189950209</t>
+          <t>57487992</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/189950209</t>
+          <t>https://m.place.naver.com/place/57487992</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -3908,29 +3928,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>네일존 이마트연제점</t>
+          <t>네일콕</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>nailzone__@naver.com</t>
+          <t>zwonii@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1448-9396</t>
+          <t>0507-1461-8217</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 89 이마트 연제점 3층</t>
+          <t>부산광역시 연제구 중앙대로1124번길 20 2층 내부</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailzone__</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3940,12 +3960,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3961,17 +3981,17 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>220</v>
+        <v>10</v>
       </c>
       <c r="Q38" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="R38" t="n">
-        <v>254</v>
+        <v>16</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3980,17 +4000,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>1531070526</t>
+          <t>2022960036</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1531070526</t>
+          <t>https://m.place.naver.com/place/2022960036</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4002,29 +4022,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>레푸스 연산시청점</t>
+          <t>아이앤아이 속눈썹 네일 부산연산점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>refuss_@naver.com</t>
+          <t>eyeneye_nailroom@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1443-6687</t>
+          <t>0507-1307-7896</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 시청로 26-1 2층 (베스킨라빈스건물)</t>
+          <t>부산광역시 연제구 연수로 144 a동 1층 아이앤아이</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_yeonsan</t>
+          <t>https://www.instagram.com/bty.x0725</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4059,13 +4079,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1478</v>
+        <v>108</v>
       </c>
       <c r="Q39" t="n">
-        <v>431</v>
+        <v>58</v>
       </c>
       <c r="R39" t="n">
-        <v>1909</v>
+        <v>166</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4074,17 +4094,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1842243644</t>
+          <t>1303501565</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1842243644</t>
+          <t>https://m.place.naver.com/place/1303501565</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4096,29 +4116,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>페브네일</t>
+          <t>티우네일</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>yearning1128@naver.com</t>
+          <t>hdaek10@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1375-8044</t>
+          <t>0507-1361-8683</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 62-17 1층 페브네일</t>
+          <t>부산광역시 연제구 과정로343번길 22 B동 101호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/feb_nail</t>
+          <t>https://www.instagram.com/t.woo_nail</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4153,13 +4173,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>230</v>
+        <v>128</v>
       </c>
       <c r="Q40" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R40" t="n">
-        <v>242</v>
+        <v>144</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4168,17 +4188,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1968946087</t>
+          <t>1428190568</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1968946087</t>
+          <t>https://m.place.naver.com/place/1428190568</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4190,29 +4210,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>벨라티뷰티 부산시청점</t>
+          <t>네일커브</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>mijooaa@naver.com</t>
+          <t>nailcurve@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1477-0829</t>
+          <t>0507-1363-0436</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신촌로 20 2층</t>
+          <t>부산광역시 연제구 과정로343번길 9 1층 네일커브</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vellati_b?igsh=MWQ2NXlvN2J0Zmw2NQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/nail__cv</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4247,13 +4267,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="Q41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R41" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4262,17 +4282,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2002445034</t>
+          <t>1692126809</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002445034</t>
+          <t>https://m.place.naver.com/place/1692126809</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4284,39 +4304,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>네일 오 그레이</t>
+          <t>꼭대기네일</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ururu007@naver.com</t>
+          <t>foresten@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1469-0621</t>
+          <t>0507-1340-4140</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로17번길 46 1층</t>
+          <t>부산광역시 연제구 화지로 95 거제청구하이츠아파트 상가동 1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Sdpxmxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4332,22 +4352,22 @@
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>353</v>
+        <v>22</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>357</v>
+        <v>22</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4356,17 +4376,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1842181845</t>
+          <t>1056754569</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1842181845</t>
+          <t>https://m.place.naver.com/place/1056754569</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4378,29 +4398,25 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>라움네일</t>
+          <t>오브네일</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>brcomm0371@naver.com</t>
+          <t>ofrang@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>0507-1445-8116</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로73번길 4 1층 라움네일</t>
+          <t>부산광역시 연제구 중앙천로4번길 5 1층 102호</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_raum__nail?igsh=MThxa3BoYmF1cGR0YQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/_ove.nail?igsh=aWdkcjE3bDZiaHFi</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4435,13 +4451,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="Q43" t="n">
         <v>3</v>
       </c>
       <c r="R43" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4450,17 +4466,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1012943186</t>
+          <t>1870621262</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012943186</t>
+          <t>https://m.place.naver.com/place/1870621262</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4472,29 +4488,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>마이네일</t>
+          <t>레푸스 연산시청점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>mynail_busan@naver.com</t>
+          <t>refuss_@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>051-851-2458</t>
+          <t>0507-1443-6687</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 40 e편한세상 연산 더퍼스트상가 1층</t>
+          <t>부산광역시 연제구 시청로 26-1 2층 (베스킨라빈스건물)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mynail_busan</t>
+          <t>https://www.instagram.com/refuss_yeonsan</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4509,7 +4525,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4529,13 +4545,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>135</v>
+        <v>1481</v>
       </c>
       <c r="Q44" t="n">
-        <v>155</v>
+        <v>432</v>
       </c>
       <c r="R44" t="n">
-        <v>290</v>
+        <v>1913</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4544,17 +4560,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>36234466</t>
+          <t>1842243644</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36234466</t>
+          <t>https://m.place.naver.com/place/1842243644</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4566,29 +4582,25 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>유화네일 부산시청점</t>
+          <t>뷰티투미</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>zkscy711@naver.com</t>
+          <t>beauty_to_mi@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>0507-1427-6564</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로 81-17 1층 102호</t>
+          <t>부산광역시 연제구 월드컵대로114번길 13 2층 뷰티투미</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuhwa__nail</t>
+          <t>https://blog.naver.com/beauty_to_mi</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4603,7 +4615,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4623,13 +4635,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="R45" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4638,17 +4650,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1340666587</t>
+          <t>1065937655</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340666587</t>
+          <t>https://m.place.naver.com/place/1065937655</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4660,29 +4672,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>엘유네일</t>
+          <t>네일시스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>kikanaa@naver.com</t>
+          <t>mjmj012@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1306-9767</t>
+          <t>0507-1409-0104</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1075번길 58 1층 엘유네일</t>
+          <t>부산광역시 연제구 거제천로124번길 48 1층 101호</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lu_nail___</t>
+          <t>https://www.instagram.com/__nailsis</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4717,13 +4729,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4732,17 +4744,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>2036505455</t>
+          <t>1498091323</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036505455</t>
+          <t>https://m.place.naver.com/place/1498091323</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4754,29 +4766,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>모브네일 연산본점</t>
+          <t>라보니 네일</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>rkfla2321@naver.com</t>
+          <t>eunberry-@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>0507-1390-9765</t>
-        </is>
-      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로 38 1층</t>
+          <t>부산광역시 연제구 거제천로87번길 30 101동 1층 106호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/spc5ofyg</t>
+          <t>https://www.instagram.com/nail_rabboni</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4802,7 +4810,7 @@
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4811,13 +4819,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>57</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4826,17 +4834,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>2006582698</t>
+          <t>1232347337</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2006582698</t>
+          <t>https://m.place.naver.com/place/1232347337</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4848,29 +4856,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>다유네일</t>
+          <t>딴네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>djbigbang@naver.com</t>
+          <t>nobleliz_@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1415-0598</t>
+          <t>0507-1413-7542</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로 39 레이카운티 2단지상가 207호</t>
+          <t>부산광역시 연제구 중앙대로1134번길 51 1층 딴네일</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dayoonail</t>
+          <t>http://instagram.com/ddan_nail7542</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4905,13 +4913,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2217</v>
+        <v>27</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R48" t="n">
-        <v>2231</v>
+        <v>30</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4920,17 +4928,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1387061591</t>
+          <t>1750949440</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1387061591</t>
+          <t>https://m.place.naver.com/place/1750949440</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -4942,29 +4950,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>코코로네일</t>
+          <t>네일룸</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>romina97@naver.com</t>
+          <t>gumi_nailroom@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1316-7319</t>
+          <t>0507-1365-2725</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로114번길 4 1층 코코로네일</t>
+          <t>부산광역시 연제구 좌수영로 225 S101동 1층 B205호 네일룸</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailroom_busan</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -4974,7 +4982,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4990,22 +4998,22 @@
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5014,17 +5022,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1258381982</t>
+          <t>1755198272</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1258381982</t>
+          <t>https://m.place.naver.com/place/1755198272</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5036,29 +5044,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>뷰티더무드네일</t>
+          <t>블랑코뷰티</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>cjsdkwls12@naver.com</t>
+          <t>estheticianjoy@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1438-2849</t>
+          <t>0507-1353-4174</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1043번길 12 2층</t>
+          <t>부산광역시 연제구 과정로 166 1층 블랑코뷰티</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sgAjvNkg</t>
+          <t>https://open.kakao.com/o/sOUjZO1c</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5089,17 +5097,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="Q50" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="R50" t="n">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5108,17 +5116,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1636008279</t>
+          <t>1657028472</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636008279</t>
+          <t>https://m.place.naver.com/place/1657028472</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5130,29 +5138,29 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>히니네일 부산연산점</t>
+          <t>채움네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>yuu_ja@naver.com</t>
+          <t>rhdwnsla5656@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0507-1391-1454</t>
+          <t>0507-1340-9768</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1130 연산동 SK VIE W 2단지 1층 114호</t>
+          <t>부산광역시 연제구 월드컵대로 7 2층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heeni_nail</t>
+          <t>https://www.instagram.com/yoming22</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5187,13 +5195,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="R51" t="n">
-        <v>136</v>
+        <v>14</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5202,17 +5210,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1114751434</t>
+          <t>1801826590</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114751434</t>
+          <t>https://m.place.naver.com/place/1801826590</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5224,29 +5232,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>네일포유</t>
+          <t>라루즈살롱</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nail_for_u@naver.com</t>
+          <t>boram1646@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1480-6706</t>
+          <t>0507-1388-3851</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 금용로 5 1층</t>
+          <t>부산광역시 연제구 중앙대로 1130 SK뷰 2단지 2층 201호</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_for_you_6694</t>
+          <t>https://www.instagram.com/laluz.salon/</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5281,13 +5289,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>13</v>
+        <v>374</v>
       </c>
       <c r="Q52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>14</v>
+        <v>377</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5296,17 +5304,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1173016573</t>
+          <t>1358321177</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1173016573</t>
+          <t>https://m.place.naver.com/place/1358321177</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5318,29 +5326,25 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>어썸네일</t>
+          <t>네일이야기</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>loves0226@naver.com</t>
+          <t>mimi7807@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0507-1366-2967</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 안연로 24 1층</t>
+          <t>부산광역시 연제구 배산로23번길 4</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/awesome_nail_2967</t>
+          <t>https://blog.naver.com/mimi7807</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5355,7 +5359,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5375,13 +5379,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="Q53" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="R53" t="n">
-        <v>103</v>
+        <v>26</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5390,17 +5394,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1637674026</t>
+          <t>1983677901</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1637674026</t>
+          <t>https://m.place.naver.com/place/1983677901</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5412,29 +5416,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일룸</t>
+          <t>네일 드네쥬</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>gumi_nailroom@naver.com</t>
+          <t>denejue@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1365-2725</t>
+          <t>0507-1312-5886</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 좌수영로 225 S101동 1층 B205호 네일룸</t>
+          <t>부산광역시 연제구 토곡로 37 1층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailroom_busan</t>
+          <t>https://www.instagram.com/nail_denejue?igsh=dHRxMHR2aHJidjg0&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5460,7 +5464,7 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5469,13 +5473,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="Q54" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="R54" t="n">
-        <v>79</v>
+        <v>167</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5484,17 +5488,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1755198272</t>
+          <t>1892993746</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1755198272</t>
+          <t>https://m.place.naver.com/place/1892993746</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5506,25 +5510,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>네일이야기</t>
+          <t>마이네일</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mimi7807@naver.com</t>
+          <t>mynail_busan@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>051-851-2458</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 배산로23번길 4</t>
+          <t>부산광역시 연제구 반송로 40 e편한세상 연산 더퍼스트상가 1층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mimi7807</t>
+          <t>https://blog.naver.com/mynail_busan</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5559,13 +5567,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>5</v>
+        <v>135</v>
       </c>
       <c r="Q55" t="n">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="R55" t="n">
-        <v>26</v>
+        <v>290</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5574,17 +5582,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1983677901</t>
+          <t>36234466</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1983677901</t>
+          <t>https://m.place.naver.com/place/36234466</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5596,29 +5604,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>모모네일</t>
+          <t>썸네일</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>iii0701@naver.com</t>
+          <t>taiji0929@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1334-5238</t>
+          <t>051-852-4153</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 명륜로2번길 32 3층 모모네일</t>
+          <t>부산광역시 연제구 고분로 16 썸네일</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/taiji0929</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5628,7 +5636,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -5649,17 +5657,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>317</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5668,17 +5676,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1664773879</t>
+          <t>35243970</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664773879</t>
+          <t>https://m.place.naver.com/place/35243970</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5690,29 +5698,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일 드네쥬</t>
+          <t>네일맑음</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>denejue@naver.com</t>
+          <t>s1514@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>0507-1312-5886</t>
-        </is>
-      </c>
+      <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 토곡로 37 1층</t>
+          <t>부산광역시 연제구 연수로 204-1 1층 네일맑음</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_denejue?igsh=dHRxMHR2aHJidjg0&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5722,7 +5726,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5743,17 +5747,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="R57" t="n">
-        <v>167</v>
+        <v>13</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5762,17 +5766,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1892993746</t>
+          <t>1944625741</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1892993746</t>
+          <t>https://m.place.naver.com/place/1944625741</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5784,29 +5788,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>네일앤미</t>
+          <t>라르네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>nkm1004@naver.com</t>
+          <t>dlqnsr_@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1329-5080</t>
+          <t>0507-1375-1612</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 282 청목파르테논705호</t>
+          <t>부산광역시 연제구 신금로23번길 56 1층 라르네일</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/nailnmi</t>
+          <t>https://www.instagram.com/nail_lart_</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5841,13 +5845,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>55</v>
+        <v>253</v>
       </c>
       <c r="Q58" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="R58" t="n">
-        <v>103</v>
+        <v>261</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5856,17 +5860,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>121674192</t>
+          <t>1477228054</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/121674192</t>
+          <t>https://m.place.naver.com/place/1477228054</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5878,25 +5882,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>뷰티투미</t>
+          <t>가온네일</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>beauty_to_mi@naver.com</t>
+          <t>leedmswh8898@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>0507-1345-8019</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로114번길 13 2층 뷰티투미</t>
+          <t>부산광역시 연제구 거제천로 82 삼정그린코아포레스트 상가동 210호</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/beauty_to_mi</t>
+          <t>https://www.instagram.com/gaonnail_/</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5911,7 +5919,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5931,13 +5939,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>17</v>
+        <v>191</v>
       </c>
       <c r="Q59" t="n">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="R59" t="n">
-        <v>46</v>
+        <v>263</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5946,17 +5954,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1065937655</t>
+          <t>1960748053</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065937655</t>
+          <t>https://m.place.naver.com/place/1960748053</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -5968,29 +5976,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>썸네일</t>
+          <t>신지네일&amp;메이크업 연산동점</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>taiji0929@naver.com</t>
+          <t>springonion_eggs@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>051-852-4153</t>
+          <t>0507-1309-9627</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로 16 썸네일</t>
+          <t>부산광역시 연제구 중앙대로1124번길 15 1층상가</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taiji0929</t>
+          <t>https://www.instagram.com/shinzinail/</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6025,13 +6033,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>43</v>
+        <v>181</v>
       </c>
       <c r="Q60" t="n">
-        <v>274</v>
+        <v>294</v>
       </c>
       <c r="R60" t="n">
-        <v>317</v>
+        <v>475</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6040,17 +6048,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>35243970</t>
+          <t>1776187392</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35243970</t>
+          <t>https://m.place.naver.com/place/1776187392</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6062,34 +6070,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>더킴스네일뷰티</t>
+          <t>노니네일</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>rlawlgo85@naver.com</t>
+          <t>siunim@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>0507-1420-5259</t>
-        </is>
-      </c>
+      <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 19 신종빌딩 5층</t>
+          <t>부산광역시 연제구 월드컵대로73번길 82 풀잎하우스빌 1층 101호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thekims2012?igsh=Nmp3ZWN4NmRrYjA5&amp;utm_source=qr</t>
+          <t>http://pf.kakao.com/_Wgxnzxj</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -6110,7 +6114,7 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6119,13 +6123,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>232</v>
+        <v>35</v>
       </c>
       <c r="Q61" t="n">
-        <v>957</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>1189</v>
+        <v>36</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6134,17 +6138,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>31098912</t>
+          <t>1561653317</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31098912</t>
+          <t>https://m.place.naver.com/place/1561653317</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6156,30 +6160,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>라보니 네일</t>
+          <t>네일앤미</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>eunberry-@naver.com</t>
+          <t>nkm1004@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0507-1329-5080</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로87번길 30 101동 1층 106호</t>
+          <t>부산광역시 연제구 월드컵대로 282 청목파르테논705호</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_rabboni</t>
+          <t>https://smartstore.naver.com/nailnmi</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6209,13 +6217,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="R62" t="n">
-        <v>6</v>
+        <v>103</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6224,17 +6232,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1232347337</t>
+          <t>121674192</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1232347337</t>
+          <t>https://m.place.naver.com/place/121674192</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6246,29 +6254,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>네일커브</t>
+          <t>라온네일</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>nailcurve@naver.com</t>
+          <t>yutin60537@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1363-0436</t>
+          <t>0507-1364-1656</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로343번길 9 1층 네일커브</t>
+          <t>부산광역시 연제구 고분로32번길 23 1층</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__cv</t>
+          <t>http://instagram.com/la_on_nail</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6303,13 +6311,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="Q63" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="R63" t="n">
-        <v>109</v>
+        <v>170</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6318,17 +6326,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1692126809</t>
+          <t>1100502822</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692126809</t>
+          <t>https://m.place.naver.com/place/1100502822</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6340,29 +6348,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>네일,별</t>
+          <t>클래시네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>dkfzhdspdlf@naver.com</t>
+          <t>classynail_@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1379-2261</t>
+          <t>0507-1430-1890</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로19번길 46 2층</t>
+          <t>부산광역시 연제구 연제로 30 상가 203동 105호</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_byeol_</t>
+          <t>https://blog.naver.com/classynail_</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6377,7 +6385,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6397,13 +6405,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="Q64" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="R64" t="n">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6412,17 +6420,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1252164677</t>
+          <t>1456426601</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252164677</t>
+          <t>https://m.place.naver.com/place/1456426601</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6434,29 +6442,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>랑뷰티</t>
+          <t>네일포유</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>bbakggu0723@naver.com</t>
+          <t>nail_for_u@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1490-3542</t>
+          <t>0507-1480-6706</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로255번길 48 1층</t>
+          <t>부산광역시 연제구 금용로 5 1층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_for_you_6694</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6466,7 +6474,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -6487,17 +6495,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6506,17 +6514,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>2088276975</t>
+          <t>1173016573</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2088276975</t>
+          <t>https://m.place.naver.com/place/1173016573</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6528,29 +6536,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>네일콕</t>
+          <t>제니엘뷰티</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>zwonii@naver.com</t>
+          <t>jennyelbeauty@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1461-8217</t>
+          <t>0507-1328-8789</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1124번길 20 2층 내부</t>
+          <t>부산광역시 연제구 중앙대로 1077 메디컬시티 12층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/jennyelbeauty</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6560,12 +6568,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6581,17 +6589,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P66" t="n">
         <v>10</v>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>207</v>
       </c>
       <c r="R66" t="n">
-        <v>15</v>
+        <v>217</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6600,17 +6608,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>2022960036</t>
+          <t>1580331994</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2022960036</t>
+          <t>https://m.place.naver.com/place/1580331994</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6622,29 +6630,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일예쁨</t>
+          <t>네일커밍</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>maeilyepboom@naver.com</t>
+          <t>coming230201@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1463-5608</t>
+          <t>0507-1327-0497</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연제로 21 힐스테이트상가 2층 203호(홍익노무법인건물)</t>
+          <t>부산광역시 연제구 과정로208번길 16</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/adst8888</t>
+          <t>https://blog.naver.com/coming230201</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6659,7 +6667,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6679,13 +6687,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>66</v>
+        <v>160</v>
       </c>
       <c r="Q67" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="R67" t="n">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6694,17 +6702,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1462213612</t>
+          <t>1185455703</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1462213612</t>
+          <t>https://m.place.naver.com/place/1185455703</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6716,29 +6724,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nail빛</t>
+          <t>벨루아뷰티</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>triple-b@naver.com</t>
+          <t>sh26888@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>0507-1322-9781</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 80 연산동일동미라주 106동 1층상가 네일빛</t>
+          <t>부산광역시 연제구 쌍미천로 147 3층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_ybit</t>
+          <t>https://www.instagram.com/bellua_beauty?igsh=MWltZ2hrbWZpYzAxdw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6773,13 +6777,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>300</v>
+        <v>45</v>
       </c>
       <c r="Q68" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="R68" t="n">
-        <v>328</v>
+        <v>63</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6788,17 +6792,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>1478119147</t>
+          <t>2086054910</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478119147</t>
+          <t>https://m.place.naver.com/place/2086054910</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6810,29 +6814,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>바비랑네일</t>
+          <t>네일,그날</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>rladbrud8791@naver.com</t>
+          <t>nahe0904@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>051-867-9910</t>
+          <t>0507-1476-4141</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1039번길 15 . 1층</t>
+          <t>부산광역시 연제구 연수로 125-1 2층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/babirang_</t>
+          <t>http://instagram.com/nail_theday.__</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6867,13 +6871,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="Q69" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R69" t="n">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6882,17 +6886,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>950132087</t>
+          <t>1061426000</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/950132087</t>
+          <t>https://m.place.naver.com/place/1061426000</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6904,29 +6908,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>제니엘뷰티</t>
+          <t>이유네일 부산연산점</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>jennyelbeauty@naver.com</t>
+          <t>todnfksp1@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1328-8789</t>
+          <t>0507-1357-5036</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1077 메디컬시티 12층</t>
+          <t>부산광역시 연제구 중앙대로 1130 2층 206호</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jennyelbeauty</t>
+          <t>https://www.instagram.com/leeyu_nail_</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6941,7 +6945,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6961,13 +6965,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>10</v>
+        <v>491</v>
       </c>
       <c r="Q70" t="n">
-        <v>207</v>
+        <v>45</v>
       </c>
       <c r="R70" t="n">
-        <v>217</v>
+        <v>536</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6976,17 +6980,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1580331994</t>
+          <t>1682866660</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1580331994</t>
+          <t>https://m.place.naver.com/place/1682866660</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -6998,30 +7002,34 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>네일블리진</t>
+          <t>보니또네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>rkmgl2622@naver.com</t>
+          <t>ourcutelove@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>0507-1479-7034</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1039-1 3층</t>
+          <t>부산광역시 연제구 고분로 200 상가동 107호</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YxbxmQT</t>
+          <t>https://www.instagram.com/bonitto__nail</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -7042,7 +7050,7 @@
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7051,13 +7059,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="Q71" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7066,17 +7074,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1051433565</t>
+          <t>1222997854</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1051433565</t>
+          <t>https://m.place.naver.com/place/1222997854</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7088,29 +7096,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>네일스튜디오 바이 민</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>seongaya@naver.com</t>
+          <t>jjuahlee@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>051-939-8726</t>
+          <t>0507-1305-1030</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 안연로 33 상가 A동 110호</t>
+          <t>부산광역시 연제구 쌍미천로151번길 17</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/seongaya</t>
+          <t>http://instagram.com/coconail_mj</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7125,7 +7133,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -7145,13 +7153,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R72" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7160,17 +7168,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1709352377</t>
+          <t>1043623932</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1709352377</t>
+          <t>https://m.place.naver.com/place/1043623932</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7182,29 +7190,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>더네일</t>
+          <t>오드레 네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>thenail_@naver.com</t>
+          <t>seunjeung@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1311-1145</t>
+          <t>0507-1436-2772</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제대로178번길 55-1 더네일</t>
+          <t>부산광역시 연제구 아시아드대로22번길 36 401동 103일부호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/the_nail120</t>
+          <t>https://www.instagram.com/odrenail</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7230,7 +7238,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7239,13 +7247,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="Q73" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R73" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7254,17 +7262,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1230694056</t>
+          <t>1326125631</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230694056</t>
+          <t>https://m.place.naver.com/place/1326125631</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7276,29 +7284,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>네일,그날</t>
+          <t>더혜뷰티 연산양정점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>nahe0904@naver.com</t>
+          <t>seoin1999@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1476-4141</t>
+          <t>0507-1471-0417</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 125-1 2층</t>
+          <t>부산광역시 연제구 연수로87번길 3 3층</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_theday.__</t>
+          <t>http://instagram.com/the_hye_beauty</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7333,13 +7341,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>97</v>
+        <v>488</v>
       </c>
       <c r="Q74" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="R74" t="n">
-        <v>109</v>
+        <v>513</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7348,17 +7356,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1061426000</t>
+          <t>1695025021</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061426000</t>
+          <t>https://m.place.naver.com/place/1695025021</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7370,29 +7378,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>이유네일 부산연산점</t>
+          <t>네일바</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>todnfksp1@naver.com</t>
+          <t>rosamatt@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0507-1357-5036</t>
+          <t>051-758-3963</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1130 2층 206호</t>
+          <t>부산광역시 연제구 과정로 80 1층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/leeyu_nail_</t>
+          <t>http://instagram.com/nail_bar._</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7427,13 +7435,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>491</v>
+        <v>57</v>
       </c>
       <c r="Q75" t="n">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="R75" t="n">
-        <v>536</v>
+        <v>121</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7442,17 +7450,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>1682866660</t>
+          <t>32333430</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682866660</t>
+          <t>https://m.place.naver.com/place/32333430</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7464,29 +7472,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>유니스네일뷰티</t>
+          <t>모브네일 연산본점</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>soyun4241@naver.com</t>
+          <t>rkfla2321@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0507-1382-4241</t>
+          <t>0507-1390-9765</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로230번길 61 1층 유니스네일뷰티</t>
+          <t>부산광역시 연제구 고분로 38 1층</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/artist_yunice</t>
+          <t>https://open.kakao.com/o/spc5ofyg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7512,7 +7520,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7521,13 +7529,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>136</v>
+        <v>57</v>
       </c>
       <c r="Q76" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>167</v>
+        <v>60</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7536,17 +7544,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>1725318910</t>
+          <t>2006582698</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1725318910</t>
+          <t>https://m.place.naver.com/place/2006582698</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7558,29 +7566,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>네일르엔</t>
+          <t>온 네일</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>reruns_@naver.com</t>
+          <t>guswnwnwn@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1357-6422</t>
+          <t>0507-1446-3360</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 140 상진빌딩 2층</t>
+          <t>부산광역시 연제구 시청로 12 더샵씨티애비뉴2차 상가 2층215호</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_le.n</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7590,7 +7598,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7606,22 +7614,22 @@
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>184</v>
+        <v>36</v>
       </c>
       <c r="Q77" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="R77" t="n">
-        <v>204</v>
+        <v>60</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7630,17 +7638,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>1665472449</t>
+          <t>189950209</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1665472449</t>
+          <t>https://m.place.naver.com/place/189950209</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7652,29 +7660,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>라르네일</t>
+          <t>네일가예쁨</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>dlqnsr_@naver.com</t>
+          <t>narea7909@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>0507-1375-1612</t>
-        </is>
-      </c>
+      <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로23번길 56 1층 라르네일</t>
+          <t>부산광역시 연제구 거제천로 233 주상가동 103-1호</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lart_</t>
+          <t>http://www.instagram.com/nail_gayeppeum</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7709,13 +7713,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>252</v>
+        <v>7</v>
       </c>
       <c r="Q78" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R78" t="n">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7724,17 +7728,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1477228054</t>
+          <t>1192185627</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1477228054</t>
+          <t>https://m.place.naver.com/place/1192185627</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7746,29 +7750,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>루미가넷 네일존 사직</t>
+          <t>원더우먼 네일</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>webmore@naver.com</t>
+          <t>sh88351@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>070-7012-9336</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 종합운동장로 7 아시아드 홈플러스 지하1층 네일존</t>
+          <t>부산광역시 연제구 월드컵대로 76 모티더베스트빌 상가 103호</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/wonder8686774</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P79" t="n">
         <v>3</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R79" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7818,17 +7818,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1179495995</t>
+          <t>1190599964</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179495995</t>
+          <t>https://m.place.naver.com/place/1190599964</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7840,25 +7840,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>네일맑음</t>
+          <t>리본네일 부산시청점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>s1514@naver.com</t>
+          <t>girljakpoom@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>0507-1442-5066</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 204-1 1층 네일맑음</t>
+          <t>부산광역시 연제구 중앙대로1043번길 56 2층 리본네일 부산시청점</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/girljakpoom</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7868,12 +7872,12 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7889,17 +7893,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="Q80" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R80" t="n">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7908,17 +7912,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1944625741</t>
+          <t>1260057809</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944625741</t>
+          <t>https://m.place.naver.com/place/1260057809</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -7930,29 +7934,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>네일 더 드리밍 연산시청점</t>
+          <t>영네일</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ssongs_yummy@naver.com</t>
+          <t>cy2403@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1347-4595</t>
+          <t>051-504-0506</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로 8 1층 네일 더 드리밍 연산시청점</t>
+          <t>부산광역시 연제구 아시아드대로 95</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_the.dreaming</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7962,7 +7966,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7983,17 +7987,17 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>229</v>
+        <v>7</v>
       </c>
       <c r="Q81" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="R81" t="n">
-        <v>247</v>
+        <v>21</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8002,17 +8006,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1491294937</t>
+          <t>1168856867</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1491294937</t>
+          <t>https://m.place.naver.com/place/1168856867</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8024,25 +8028,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>츄제이네일 부산연산점</t>
+          <t>패디당</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>qhdwkzz@naver.com</t>
+          <t>pedidang@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>0507-1302-3954</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1130 SK뷰 2단지 2층 216호 츄제이네일</t>
+          <t>부산광역시 연제구 거제천로 82 삼정그린코아 포레스트 상가동 2층 211호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chuuj_nail</t>
+          <t>https://www.instagram.com/pedi._.dang</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8077,13 +8085,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>225</v>
+        <v>2</v>
       </c>
       <c r="Q82" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>333</v>
+        <v>2</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8092,17 +8100,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>1173391234</t>
+          <t>2026492166</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1173391234</t>
+          <t>https://m.place.naver.com/place/2026492166</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8114,29 +8122,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>네일한날</t>
+          <t>하정수네일</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ch5502@naver.com</t>
+          <t>0hyeah6@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>0507-1402-2670</t>
-        </is>
-      </c>
+      <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 80 107동 112호</t>
+          <t>부산광역시 연제구 종합운동장로12번길 34</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhannal2670</t>
+          <t>http://instagram.com/hjsnail</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8171,13 +8175,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>252</v>
+        <v>16</v>
       </c>
       <c r="Q83" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>306</v>
+        <v>17</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8186,17 +8190,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1298434527</t>
+          <t>1060527554</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1298434527</t>
+          <t>https://m.place.naver.com/place/1060527554</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8208,12 +8212,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>노니네일</t>
+          <t>바이요니네일</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>siunim@naver.com</t>
+          <t>kitty_log@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -8221,17 +8225,17 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로73번길 82 풀잎하우스빌 1층 101호</t>
+          <t>부산광역시 연제구 중앙천로 77-2 1층</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Wgxnzxj</t>
+          <t>http://instagram.com/byyoni__nail</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -8252,7 +8256,7 @@
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8261,13 +8265,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>35</v>
+        <v>460</v>
       </c>
       <c r="Q84" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R84" t="n">
-        <v>36</v>
+        <v>467</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8276,17 +8280,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1561653317</t>
+          <t>1418772825</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1561653317</t>
+          <t>https://m.place.naver.com/place/1418772825</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8298,29 +8302,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>리본네일 부산시청점</t>
+          <t>네일언니 by JU</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>girljakpoom@naver.com</t>
+          <t>amelie1223@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>0507-1442-5066</t>
-        </is>
-      </c>
+      <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1043번길 56 2층 리본네일 부산시청점</t>
+          <t>부산광역시 연제구 월드컵대로 221-7</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/girljakpoom</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P85" t="n">
-        <v>141</v>
+        <v>3</v>
       </c>
       <c r="Q85" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8370,17 +8370,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1260057809</t>
+          <t>637720481</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260057809</t>
+          <t>https://m.place.naver.com/place/637720481</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8392,34 +8392,34 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>오늘의네일</t>
+          <t>네일 오 그레이</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>redcherry88@naver.com</t>
+          <t>ururu007@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1398-3444</t>
+          <t>0507-1469-0621</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로 254 1층</t>
+          <t>부산광역시 연제구 신금로17번길 46 1층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>http://instagram.com/cny3444</t>
+          <t>http://pf.kakao.com/_Sdpxmxj</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -8440,7 +8440,7 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -8449,13 +8449,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>5</v>
+        <v>354</v>
       </c>
       <c r="Q86" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="R86" t="n">
-        <v>32</v>
+        <v>358</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8464,17 +8464,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1838257805</t>
+          <t>1842181845</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1838257805</t>
+          <t>https://m.place.naver.com/place/1842181845</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8486,29 +8486,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>가온네일</t>
+          <t>랑뷰티</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>leedmswh8898@naver.com</t>
+          <t>bbakggu0723@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1345-8019</t>
+          <t>0507-1490-3542</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 82 삼정그린코아포레스트 상가동 210호</t>
+          <t>부산광역시 연제구 거제천로255번길 48 1층</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gaonnail_/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8539,17 +8539,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>263</v>
+        <v>0</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8558,17 +8558,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>1960748053</t>
+          <t>2088276975</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1960748053</t>
+          <t>https://m.place.naver.com/place/2088276975</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8580,25 +8580,29 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JM NAIL</t>
+          <t>엔피케어 부산연산점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>qkrwjddms105@naver.com</t>
+          <t>np_care@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>0507-1449-2096</t>
+        </is>
+      </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 258 연산해수피아 2층</t>
+          <t>부산광역시 연제구 중앙대로 1114 4층</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jmnail0104</t>
+          <t>https://www.youtube.com/@NPCARE_</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8613,7 +8617,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8633,13 +8637,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>579</v>
       </c>
       <c r="Q88" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="R88" t="n">
-        <v>39</v>
+        <v>716</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8648,17 +8652,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1875116182</t>
+          <t>1204729944</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875116182</t>
+          <t>https://m.place.naver.com/place/1204729944</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8670,29 +8674,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>뷰티빛담</t>
+          <t>JM NAIL</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>dksdudtjs1234@naver.com</t>
+          <t>qkrwjddms105@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>0507-1337-6219</t>
-        </is>
-      </c>
+      <c r="E89" t="inlineStr"/>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로 7 104호</t>
+          <t>부산광역시 연제구 거제천로 258 연산해수피아 2층</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://instagram.com/beauty_bitdam?utm_medium=copy_link</t>
+          <t>https://www.instagram.com/jmnail0104</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8727,13 +8727,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>553</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="R89" t="n">
-        <v>561</v>
+        <v>39</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8742,17 +8742,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1482685574</t>
+          <t>1875116182</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1482685574</t>
+          <t>https://m.place.naver.com/place/1875116182</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8764,25 +8764,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>네일가예쁨</t>
+          <t>꼼네일</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>narea7909@naver.com</t>
+          <t>immire@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0507-1319-4713</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 233 주상가동 103-1호</t>
+          <t>부산광역시 연제구 법원북로 13 쌍용스윗닷홈 상가 105호</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_gayeppeum</t>
+          <t>http://instagram.com/nail_ggom</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8808,7 +8812,7 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8817,13 +8821,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="Q90" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="R90" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8832,17 +8836,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1192185627</t>
+          <t>1200894164</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192185627</t>
+          <t>https://m.place.naver.com/place/1200894164</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8854,34 +8858,34 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>리앤뷰티네일</t>
+          <t>올바른 네일&amp;브로우</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>wnqkf517@naver.com</t>
+          <t>stylemusee@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1341-3798</t>
+          <t>0507-1416-7885</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 105-1 3층 리앤뷰티네일</t>
+          <t>부산광역시 연제구 거제천로 82 205호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/</t>
+          <t>https://www.instagram.com/ab_browlab</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -8891,7 +8895,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -8911,13 +8915,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="Q91" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="R91" t="n">
-        <v>11</v>
+        <v>213</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8926,17 +8930,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1056219004</t>
+          <t>1021114766</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1056219004</t>
+          <t>https://m.place.naver.com/place/1021114766</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -8948,29 +8952,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>네일이냥</t>
+          <t>네일오예</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>nail-nyang@naver.com</t>
+          <t>efjekkk0888@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>051-867-4377</t>
+          <t>0507-1424-0360</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로294번길 10 네일이냥 (동원베네스트, 상가)</t>
+          <t>부산광역시 연제구 해맞이로67번길 23 102호</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail-nyang</t>
+          <t>https://www.instagram.com/nail_o.yeah?igsh=MTBrcDN2OHM5djY1cQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8985,7 +8989,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -9005,13 +9009,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="Q92" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R92" t="n">
-        <v>38</v>
+        <v>140</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9020,17 +9024,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>1081723048</t>
+          <t>2070499527</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1081723048</t>
+          <t>https://m.place.naver.com/place/2070499527</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9042,29 +9046,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>티우네일</t>
+          <t>에스네일</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>hdaek10@naver.com</t>
+          <t>7gonggu@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>0507-1361-8683</t>
+          <t>0507-1303-4143</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로343번길 22 B동 101호</t>
+          <t>부산광역시 연제구 거제천로 258 연산해수피아 1층 105호</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/t.woo_nail</t>
+          <t>https://blog.naver.com/7gonggu</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9079,7 +9083,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9099,13 +9103,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>128</v>
+        <v>5</v>
       </c>
       <c r="Q93" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R93" t="n">
-        <v>144</v>
+        <v>15</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9114,17 +9118,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1428190568</t>
+          <t>1772096643</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1428190568</t>
+          <t>https://m.place.naver.com/place/1772096643</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9136,29 +9140,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>보니또네일</t>
+          <t>모어브 네일스튜디오</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ourcutelove@naver.com</t>
+          <t>pilates_youl@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1479-7034</t>
+          <t>0507-1382-2699</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로 200 상가동 107호</t>
+          <t>부산광역시 연제구 중앙대로1038번길 40 행복주택2단지 근린생활시설D동 201호</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bonitto__nail</t>
+          <t>https://www.instagram.com/moav_nail</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9193,13 +9197,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="Q94" t="n">
         <v>3</v>
       </c>
       <c r="R94" t="n">
-        <v>53</v>
+        <v>158</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9208,17 +9212,17 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1222997854</t>
+          <t>1806276546</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222997854</t>
+          <t>https://m.place.naver.com/place/1806276546</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9230,12 +9234,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>원더우먼 네일</t>
+          <t>츄제이네일 부산연산점</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>sh88351@naver.com</t>
+          <t>qhdwkzz@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
@@ -9243,12 +9247,12 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 76 모티더베스트빌 상가 103호</t>
+          <t>부산광역시 연제구 중앙대로 1130 SK뷰 2단지 2층 216호 츄제이네일</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wonder8686774</t>
+          <t>https://www.instagram.com/chuuj_nail</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9283,13 +9287,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>3</v>
+        <v>225</v>
       </c>
       <c r="Q95" t="n">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="R95" t="n">
-        <v>25</v>
+        <v>333</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9298,17 +9302,17 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1190599964</t>
+          <t>1173391234</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1190599964</t>
+          <t>https://m.place.naver.com/place/1173391234</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9320,29 +9324,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>네일시스</t>
+          <t>네일노마 연산역점</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>mjmj012@naver.com</t>
+          <t>mison0327@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1409-0104</t>
+          <t>0507-1320-0958</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로124번길 48 1층 101호</t>
+          <t>부산광역시 연제구 월드컵대로91번길 20 유림스카이 1층 101호</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nailsis</t>
+          <t>https://www.instagram.com/nailnoma</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9377,13 +9381,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>34</v>
+        <v>371</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="R96" t="n">
-        <v>34</v>
+        <v>404</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9392,17 +9396,17 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1498091323</t>
+          <t>1708779082</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1498091323</t>
+          <t>https://m.place.naver.com/place/1708779082</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9414,34 +9418,34 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>하루네일</t>
+          <t>네일 더 드리밍 연산시청점</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>luv744@naver.com</t>
+          <t>ssongs_yummy@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>051-868-7333</t>
+          <t>0507-1347-4595</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로255번가길 31 1층</t>
+          <t>부산광역시 연제구 중앙천로 8 1층 네일 더 드리밍 연산시청점</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/526220</t>
+          <t>https://www.instagram.com/nail_the.dreaming</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -9471,13 +9475,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>137</v>
+        <v>236</v>
       </c>
       <c r="Q97" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R97" t="n">
-        <v>156</v>
+        <v>254</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9486,17 +9490,17 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1884949089</t>
+          <t>1491294937</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884949089</t>
+          <t>https://m.place.naver.com/place/1491294937</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9508,29 +9512,29 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>꼼네일</t>
+          <t>어썸네일</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>immire@naver.com</t>
+          <t>loves0226@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0507-1319-4713</t>
+          <t>0507-1366-2967</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 법원북로 13 쌍용스윗닷홈 상가 105호</t>
+          <t>부산광역시 연제구 안연로 24 1층</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_ggom</t>
+          <t>https://www.instagram.com/awesome_nail_2967</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9556,7 +9560,7 @@
       <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -9565,13 +9569,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="Q98" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="R98" t="n">
-        <v>48</v>
+        <v>103</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9580,17 +9584,17 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1200894164</t>
+          <t>1637674026</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200894164</t>
+          <t>https://m.place.naver.com/place/1637674026</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9602,29 +9606,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>채움네일</t>
+          <t>네일이냥</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>rhdwnsla5656@naver.com</t>
+          <t>nail-nyang@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0507-1340-9768</t>
+          <t>051-867-4377</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 7 2층</t>
+          <t>부산광역시 연제구 과정로294번길 10 네일이냥 (동원베네스트, 상가)</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yoming22</t>
+          <t>https://blog.naver.com/nail-nyang</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9639,7 +9643,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9659,13 +9663,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="Q99" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R99" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9674,17 +9678,17 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1801826590</t>
+          <t>1081723048</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1801826590</t>
+          <t>https://m.place.naver.com/place/1081723048</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9696,29 +9700,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>효리의빛나는네일</t>
+          <t>소르베네일 부산시청점</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>mongmo23@naver.com</t>
+          <t>oladeoro@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1341-9746</t>
+          <t>0507-1487-4679</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제대로 275 상가동 지1층 107호</t>
+          <t>부산광역시 연제구 중앙대로1038번길 40 근린생활시설 D동 2층 208호</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TZUW7eqR3</t>
+          <t>https://pf.kakao.com/_xdHhHn</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -9728,7 +9732,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -9753,14 +9757,14 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="Q100" t="n">
+        <v>1</v>
+      </c>
+      <c r="R100" t="n">
         <v>17</v>
       </c>
-      <c r="R100" t="n">
-        <v>177</v>
-      </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>X</t>
@@ -9768,17 +9772,17 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>2040725905</t>
+          <t>2032602450</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040725905</t>
+          <t>https://m.place.naver.com/place/2032602450</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9790,29 +9794,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>썬즈네일</t>
+          <t>뷰티더무드네일</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>suns-nail@naver.com</t>
+          <t>cjsdkwls12@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1468-2628</t>
+          <t>0507-1438-2849</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로28번길 9 상가동 1층 209호 썬즈네일</t>
+          <t>부산광역시 연제구 중앙대로1043번길 12 2층</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sunsnail</t>
+          <t>https://open.kakao.com/o/sgAjvNkg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9838,7 +9842,7 @@
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -9847,13 +9851,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="Q101" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="R101" t="n">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9862,17 +9866,17 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1468663766</t>
+          <t>1636008279</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468663766</t>
+          <t>https://m.place.naver.com/place/1636008279</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9884,29 +9888,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>라루즈살롱</t>
+          <t>네시일분 예뻐지는시간</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>boram1646@naver.com</t>
+          <t>alal7667@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0507-1388-3851</t>
+          <t>0507-1335-9404</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1130 SK뷰 2단지 2층 201호</t>
+          <t>부산광역시 연제구 과정로343번길 22 더스타a동 101호 네시일분</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/laluz.salon/</t>
+          <t>https://www.instagram.com/nesiilbun_beauty</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9941,13 +9945,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>373</v>
+        <v>38</v>
       </c>
       <c r="Q102" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="R102" t="n">
-        <v>376</v>
+        <v>54</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9956,17 +9960,17 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1358321177</t>
+          <t>1660019694</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358321177</t>
+          <t>https://m.place.naver.com/place/1660019694</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -9978,34 +9982,34 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>네일노마 연산역점</t>
+          <t>리앤뷰티네일</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>mison0327@naver.com</t>
+          <t>wnqkf517@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0507-1320-0958</t>
+          <t>0507-1341-3798</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로91번길 20 유림스카이 1층 101호</t>
+          <t>부산광역시 연제구 거제천로 105-1 3층 리앤뷰티네일</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailnoma</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10015,7 +10019,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10035,13 +10039,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>371</v>
+        <v>10</v>
       </c>
       <c r="Q103" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="R103" t="n">
-        <v>404</v>
+        <v>11</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10050,17 +10054,17 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1708779082</t>
+          <t>1056219004</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1708779082</t>
+          <t>https://m.place.naver.com/place/1056219004</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10072,29 +10076,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>마틸다네일</t>
+          <t>다유네일</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>wngml2572@naver.com</t>
+          <t>djbigbang@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0507-1363-7291</t>
+          <t>0507-1415-0598</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로 18 2층</t>
+          <t>부산광역시 연제구 아시아드대로 39 레이카운티 2단지상가 207호</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/stWnFTNg</t>
+          <t>https://www.instagram.com/dayoonail</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10120,7 +10124,7 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -10129,13 +10133,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>31</v>
+        <v>2238</v>
       </c>
       <c r="Q104" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R104" t="n">
-        <v>43</v>
+        <v>2252</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10144,17 +10148,17 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1247183274</t>
+          <t>1387061591</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1247183274</t>
+          <t>https://m.place.naver.com/place/1387061591</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10166,29 +10170,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>아이앤아이 속눈썹 네일 부산연산점</t>
+          <t>네일한날</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>eyeneye_nailroom@naver.com</t>
+          <t>ch5502@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1307-7896</t>
+          <t>0507-1402-2670</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 144 a동 1층 아이앤아이</t>
+          <t>부산광역시 연제구 반송로 80 107동 112호</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bty.x0725</t>
+          <t>https://www.instagram.com/nailhannal2670</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10223,13 +10227,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>108</v>
+        <v>255</v>
       </c>
       <c r="Q105" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="R105" t="n">
-        <v>166</v>
+        <v>309</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10238,17 +10242,17 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>1303501565</t>
+          <t>1298434527</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303501565</t>
+          <t>https://m.place.naver.com/place/1298434527</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10260,29 +10264,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>수네일아트</t>
+          <t>바나다네일</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>very_cake@naver.com</t>
+          <t>ksn0706@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0507-1400-4149</t>
+          <t>0507-1332-8909</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 명륜로2번길 7 삼익퓨처타워상가 101동 3층 311호 수네일아트</t>
+          <t>부산광역시 연제구 쌍미천로 163-1 바나다네일</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://youtube.com/</t>
+          <t>https://blog.naver.com/ksn0706</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -10297,7 +10301,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -10313,17 +10317,17 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>6</v>
+        <v>129</v>
       </c>
       <c r="Q106" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="R106" t="n">
-        <v>7</v>
+        <v>162</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10332,17 +10336,17 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>12869643</t>
+          <t>34818659</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12869643</t>
+          <t>https://m.place.naver.com/place/34818659</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10354,29 +10358,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>명월네일샵</t>
+          <t>2월11일네일</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>leekatanail@naver.com</t>
+          <t>211nail_0211@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0507-1461-1196</t>
+          <t>0507-1329-6882</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 246</t>
+          <t>부산광역시 연제구 중앙대로 1063 5층</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leekatanail</t>
+          <t>http://www.instagram.com/211_nail</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10391,7 +10395,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -10411,13 +10415,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>40</v>
+        <v>211</v>
       </c>
       <c r="Q107" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="R107" t="n">
-        <v>50</v>
+        <v>269</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10426,17 +10430,17 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1031904006</t>
+          <t>1816506274</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031904006</t>
+          <t>https://m.place.naver.com/place/1816506274</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10448,29 +10452,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>프롬제이네일</t>
+          <t>네일르엔</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>fromjnail-@naver.com</t>
+          <t>reruns_@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0507-1464-0002</t>
+          <t>0507-1357-6422</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 법원북로41번길 5 거제동원로얄듀크3차 상가동 B1층</t>
+          <t>부산광역시 연제구 월드컵대로 140 상진빌딩 2층</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fromjnail-</t>
+          <t>https://www.instagram.com/nail_le.n</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10485,7 +10489,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -10496,7 +10500,7 @@
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -10505,13 +10509,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>97</v>
+        <v>185</v>
       </c>
       <c r="Q108" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="R108" t="n">
-        <v>110</v>
+        <v>205</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10520,17 +10524,17 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>2029616168</t>
+          <t>1665472449</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029616168</t>
+          <t>https://m.place.naver.com/place/1665472449</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10542,29 +10546,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>클래시네일</t>
+          <t>더미뉴네일</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>classynail_@naver.com</t>
+          <t>mj_2023@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0507-1430-1890</t>
+          <t>0507-1460-0699</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연제로 30 상가 203동 105호</t>
+          <t>부산광역시 연제구 연수로 173 1층</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/classynail_</t>
+          <t>https://www.instagram.com/theminew.nail</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10579,7 +10583,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -10599,13 +10603,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="Q109" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="R109" t="n">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10614,17 +10618,17 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1456426601</t>
+          <t>1260374485</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456426601</t>
+          <t>https://m.place.naver.com/place/1260374485</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10718,7 +10722,7 @@
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10730,34 +10734,34 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>신지네일&amp;메이크업 연산동점</t>
+          <t>네일리크</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>springonion_eggs@naver.com</t>
+          <t>nailique25@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0507-1309-9627</t>
+          <t>0507-1449-2433</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1124번길 15 1층상가</t>
+          <t>부산광역시 연제구 월드컵대로79번길 50 1층</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shinzinail/</t>
+          <t>http://pf.kakao.com/_Vyesn</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -10778,7 +10782,7 @@
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -10787,13 +10791,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>181</v>
+        <v>316</v>
       </c>
       <c r="Q111" t="n">
-        <v>294</v>
+        <v>29</v>
       </c>
       <c r="R111" t="n">
-        <v>475</v>
+        <v>345</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10802,17 +10806,17 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1776187392</t>
+          <t>1290184827</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776187392</t>
+          <t>https://m.place.naver.com/place/1290184827</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10824,25 +10828,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>네일언니 by JU</t>
+          <t>프롬제이네일</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>amelie1223@naver.com</t>
+          <t>fromjnail-@naver.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>0507-1464-0002</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 221-7</t>
+          <t>부산광역시 연제구 법원북로41번길 5 거제동원로얄듀크3차 상가동 B1층</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/fromjnail-</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10852,12 +10860,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -10873,17 +10881,17 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="Q112" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R112" t="n">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10892,17 +10900,17 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>637720481</t>
+          <t>2029616168</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/637720481</t>
+          <t>https://m.place.naver.com/place/2029616168</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -10914,29 +10922,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>네일이나</t>
+          <t>화양연화</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>merryhunter@naver.com</t>
+          <t>glory4u_lee@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>0507-1323-8536</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로 17-1 1층</t>
+          <t>부산광역시 연제구 연안로13번길 53 1층</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_e.na?igsh=cnA0dTEwMTdjamE4</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10946,7 +10950,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -10967,17 +10971,17 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10986,17 +10990,17 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>2043892240</t>
+          <t>1137724225</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2043892240</t>
+          <t>https://m.place.naver.com/place/1137724225</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -11008,29 +11012,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>패디당</t>
+          <t>이퓨리네일 연산점</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>dlalfo0526@naver.com</t>
+          <t>ifurynail@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0507-1302-3954</t>
+          <t>0507-1356-4466</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 82 삼정그린코아 포레스트 상가동 2층 211호</t>
+          <t>부산광역시 연제구 거제천로230번길 81 유성헤네스타워 상가 1층 이퓨리네일</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pedi._.dang</t>
+          <t>https://blog.naver.com/ifurynail</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11045,7 +11049,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -11065,13 +11069,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2</v>
+        <v>249</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="R114" t="n">
-        <v>2</v>
+        <v>284</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11080,17 +11084,17 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>2026492166</t>
+          <t>1044877447</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026492166</t>
+          <t>https://m.place.naver.com/place/1044877447</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -11102,29 +11106,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>모어브 네일스튜디오</t>
+          <t>수네일아트</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>pilates_youl@naver.com</t>
+          <t>very_cake@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0507-1382-2699</t>
+          <t>0507-1400-4149</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1038번길 40 행복주택2단지 근린생활시설D동 201호</t>
+          <t>부산광역시 연제구 명륜로2번길 7 삼익퓨처타워상가 101동 3층 311호 수네일아트</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moav_nail</t>
+          <t>https://youtube.com/</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11155,17 +11159,17 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>154</v>
+        <v>6</v>
       </c>
       <c r="Q115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R115" t="n">
-        <v>157</v>
+        <v>7</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11174,17 +11178,17 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>1806276546</t>
+          <t>12869643</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806276546</t>
+          <t>https://m.place.naver.com/place/12869643</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -11196,29 +11200,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>네일,도하</t>
+          <t>네일이나</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>nsj610@naver.com</t>
+          <t>merryhunter@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0507-1498-5458</t>
+          <t>0507-1323-8536</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로11번길 114 1층 102호 네일,도하</t>
+          <t>부산광역시 연제구 신금로 17-1 1층</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_doha_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11228,7 +11232,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -11253,13 +11257,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Q116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11268,17 +11272,17 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>1673520422</t>
+          <t>2043892240</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673520422</t>
+          <t>https://m.place.naver.com/place/2043892240</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -11290,29 +11294,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>네일르누보</t>
+          <t>네일,별</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>ekgus618@naver.com</t>
+          <t>nagi96@naver.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0507-1459-8386</t>
+          <t>0507-1379-2261</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로 7 132동 204호</t>
+          <t>부산광역시 연제구 중앙천로19번길 46 2층</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_renouveau_2?igsh=MW55NjlxOTE3dGUyaw==</t>
+          <t>https://www.instagram.com/nail_byeol_</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11347,13 +11351,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>150</v>
+        <v>92</v>
       </c>
       <c r="Q117" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="R117" t="n">
-        <v>171</v>
+        <v>96</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -11362,17 +11366,17 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>1342130355</t>
+          <t>1252164677</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342130355</t>
+          <t>https://m.place.naver.com/place/1252164677</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -11384,29 +11388,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>블랑코뷰티</t>
+          <t>라로제네일</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>estheticianjoy@naver.com</t>
+          <t>brushlounge@naver.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>0507-1353-4174</t>
+          <t>0507-1343-8177</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 166 1층 블랑코뷰티</t>
+          <t>부산광역시 연제구 신금로 18 2층</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sOUjZO1c</t>
+          <t>https://open.kakao.com/o/sYvUmDpi</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -11441,13 +11445,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="Q118" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -11456,17 +11460,17 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>1657028472</t>
+          <t>2039316974</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657028472</t>
+          <t>https://m.place.naver.com/place/2039316974</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -11478,29 +11482,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>코코네일</t>
+          <t>챠밍네일 연산점</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>jjuahlee@naver.com</t>
+          <t>ghdrldbwjd1@naver.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>0507-1305-1030</t>
-        </is>
-      </c>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 쌍미천로151번길 17</t>
+          <t>부산광역시 연제구 과정로260번길 32 챠밍네일</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>http://instagram.com/coconail_mj</t>
+          <t>https://blog.naver.com/ghdrldbwjd1</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -11515,7 +11515,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -11535,13 +11535,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>8</v>
+        <v>132</v>
       </c>
       <c r="Q119" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R119" t="n">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -11550,17 +11550,205 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>1043623932</t>
+          <t>1458074178</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043623932</t>
+          <t>https://m.place.naver.com/place/1458074178</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>ONE네일</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>garam_soo@naver.com</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>0507-1349-6159</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>부산광역시 연제구 중앙대로 1049 3층</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://instagram.com/onenail_onenail?igshid=ZDdkNTZiNTM=</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P120" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>3</v>
+      </c>
+      <c r="R120" t="n">
+        <v>103</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>1153323846</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1153323846</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>제이제이네일&amp;붙임머리 거제사직점</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>kiss121127@naver.com</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>0507-1335-5968</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>부산광역시 연제구 아시아드대로 39 레이카운티 1단지상가 109호</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jj__nail</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P121" t="n">
+        <v>384</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>34</v>
+      </c>
+      <c r="R121" t="n">
+        <v>418</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>1823710447</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1823710447</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_nail/연제구_네일샵.xlsx
+++ b/naver-place-crawler/results_nail/연제구_네일샵.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V121"/>
+  <dimension ref="A1:V124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="47" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>바비랑네일</t>
+          <t>네일이냥</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rladbrud8791@naver.com</t>
+          <t>nail-nyang@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>051-867-9910</t>
+          <t>051-867-4377</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1039번길 15 . 1층</t>
+          <t>부산광역시 연제구 과정로294번길 10 네일이냥 (동원베네스트, 상가)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/babirang_</t>
+          <t>https://blog.naver.com/nail-nyang</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>950132087</t>
+          <t>1081723048</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/950132087</t>
+          <t>https://m.place.naver.com/place/1081723048</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -658,29 +658,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>모모네일</t>
+          <t>챠밍네일 연산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>brenda70@naver.com</t>
+          <t>ghdrldbwjd1@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1334-5238</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 명륜로2번길 32 3층 모모네일</t>
+          <t>부산광역시 연제구 과정로260번길 32 챠밍네일</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/ghdrldbwjd1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +686,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,17 +707,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,17 +726,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1664773879</t>
+          <t>1458074178</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1664773879</t>
+          <t>https://m.place.naver.com/place/1458074178</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -752,29 +748,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>더네일</t>
+          <t>네일 더 예쁜</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>thenail_@naver.com</t>
+          <t>dc2452@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0507-1311-1145</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제대로178번길 55-1 더네일</t>
+          <t>부산광역시 연제구 연수로218번길 2 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/the_nail120</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,7 +776,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -805,17 +797,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R4" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +816,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1230694056</t>
+          <t>2054952880</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1230694056</t>
+          <t>https://m.place.naver.com/place/2054952880</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -846,29 +838,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>뷰티빛담</t>
+          <t>온 네일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dksdudtjs1234@naver.com</t>
+          <t>guswnwnwn@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1337-6219</t>
+          <t>0507-1446-3360</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로 7 104호</t>
+          <t>부산광역시 연제구 시청로 12 더샵씨티애비뉴2차 상가 2층215호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://instagram.com/beauty_bitdam?utm_medium=copy_link</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -878,7 +870,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -899,17 +891,17 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>553</v>
+        <v>36</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="R5" t="n">
-        <v>561</v>
+        <v>60</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +910,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1482685574</t>
+          <t>189950209</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1482685574</t>
+          <t>https://m.place.naver.com/place/189950209</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -940,29 +932,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>유화네일 부산시청점</t>
+          <t>네일커브</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>zkscy711@naver.com</t>
+          <t>nailcurve@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1427-6564</t>
+          <t>0507-1363-0436</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로 81-17 1층 102호</t>
+          <t>부산광역시 연제구 과정로343번길 9 1층 네일커브</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yuhwa__nail</t>
+          <t>https://www.instagram.com/nail__cv</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -997,13 +989,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R6" t="n">
-        <v>37</v>
+        <v>109</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,17 +1004,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1340666587</t>
+          <t>1692126809</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1340666587</t>
+          <t>https://m.place.naver.com/place/1692126809</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1034,34 +1026,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>하루네일</t>
+          <t>더혜뷰티 연산양정점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>luv744@naver.com</t>
+          <t>zlwm4@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>051-868-7333</t>
+          <t>0507-1471-0417</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로255번가길 31 1층</t>
+          <t>부산광역시 연제구 연수로87번길 3 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/13/bizes/526220</t>
+          <t>http://instagram.com/the_hye_beauty</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>137</v>
+        <v>490</v>
       </c>
       <c r="Q7" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="R7" t="n">
-        <v>156</v>
+        <v>515</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1098,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1884949089</t>
+          <t>1695025021</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1884949089</t>
+          <t>https://m.place.naver.com/place/1695025021</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1120,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>투에이치 뷰티</t>
+          <t>블랑코뷰티</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jieun961216@naver.com</t>
+          <t>scisssors86@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1391-0868</t>
+          <t>0507-1353-4174</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신촌로 2 5층</t>
+          <t>부산광역시 연제구 과정로 166 1층 블랑코뷰티</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sZa5dynf</t>
+          <t>https://open.kakao.com/o/sOUjZO1c</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1181,17 +1173,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="Q8" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
       <c r="R8" t="n">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,17 +1192,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1263305975</t>
+          <t>1657028472</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1263305975</t>
+          <t>https://m.place.naver.com/place/1657028472</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1222,29 +1214,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엘유네일</t>
+          <t>뷰티빛담</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>kikanaa@naver.com</t>
+          <t>dksdudtjs1234@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1306-9767</t>
+          <t>0507-1337-6219</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1075번길 58 1층 엘유네일</t>
+          <t>부산광역시 연제구 중앙천로 7 104호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lu_nail___</t>
+          <t>https://instagram.com/beauty_bitdam?utm_medium=copy_link</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1279,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>42</v>
+        <v>553</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>42</v>
+        <v>561</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1286,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2036505455</t>
+          <t>1482685574</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2036505455</t>
+          <t>https://m.place.naver.com/place/1482685574</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1308,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>연산동_네일,더빛날</t>
+          <t>뷰티투미</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>potato00214@naver.com</t>
+          <t>beauty_to_mi@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1432-1799</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1076번길 30 1층</t>
+          <t>부산광역시 연제구 월드컵대로114번길 13 2층 뷰티투미</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_thevitnal</t>
+          <t>https://blog.naver.com/beauty_to_mi</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1353,7 +1341,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1373,13 +1361,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>129</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R10" t="n">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1376,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1424947348</t>
+          <t>1065937655</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1424947348</t>
+          <t>https://m.place.naver.com/place/1065937655</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1410,29 +1398,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>네일존 이마트연제점</t>
+          <t>네일포유</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nailzone__@naver.com</t>
+          <t>nail_for_u@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1448-9396</t>
+          <t>0507-1480-6706</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 89 이마트 연제점 3층</t>
+          <t>부산광역시 연제구 금용로 5 1층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nailzone__</t>
+          <t>https://www.instagram.com/nail_for_you_6694</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1435,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1467,13 +1455,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>221</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>255</v>
+        <v>14</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1470,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1531070526</t>
+          <t>1173016573</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1531070526</t>
+          <t>https://m.place.naver.com/place/1173016573</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1504,25 +1492,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>핑크네일</t>
+          <t>모어브 네일스튜디오</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kwy765300@naver.com</t>
+          <t>pilates_youl@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1382-2699</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 쌍미천로 120 핑크네일</t>
+          <t>부산광역시 연제구 중앙대로1038번길 40 행복주택2단지 근린생활시설D동 201호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/moav_nail</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1532,7 +1524,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1553,17 +1545,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="Q12" t="n">
-        <v>103</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>119</v>
+        <v>159</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,17 +1564,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1040392199</t>
+          <t>1806276546</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040392199</t>
+          <t>https://m.place.naver.com/place/1806276546</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1594,29 +1586,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>네일예쁨</t>
+          <t>아이앤아이 속눈썹 네일 부산연산점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>maeilyepboom@naver.com</t>
+          <t>eyeneye_nailroom@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1463-5608</t>
+          <t>0507-1307-7896</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연제로 21 힐스테이트상가 2층 203호(홍익노무법인건물)</t>
+          <t>부산광역시 연제구 연수로 144 a동 1층 아이앤아이</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/adst8888</t>
+          <t>https://www.instagram.com/bty.x0725</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1651,13 +1643,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>66</v>
+        <v>108</v>
       </c>
       <c r="Q13" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="R13" t="n">
-        <v>96</v>
+        <v>166</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,17 +1658,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1462213612</t>
+          <t>1303501565</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1462213612</t>
+          <t>https://m.place.naver.com/place/1303501565</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1762,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1782,12 +1774,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>여우네일</t>
+          <t>네일가예쁨</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>assajuju1104@naver.com</t>
+          <t>narea7909@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1795,12 +1787,12 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로 82 2층</t>
+          <t>부산광역시 연제구 거제천로 233 주상가동 103-1호</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>http://www.instagram.com/nail_gayeppeum</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1810,7 +1802,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1831,17 +1823,17 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1842,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>19997542</t>
+          <t>1192185627</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19997542</t>
+          <t>https://m.place.naver.com/place/1192185627</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1872,29 +1864,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>로제이네일</t>
+          <t>네일언니 by JU</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>permisi@naver.com</t>
+          <t>amelie1223@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1340-1354</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로191번다길 61 로제이 네일</t>
+          <t>부산광역시 연제구 월드컵대로 221-7</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ro.j_nail?igsh=MWU4ZXBiczVvaTdlaQ%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1904,7 +1892,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1925,17 +1913,17 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q16" t="n">
         <v>1</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,17 +1932,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1088938826</t>
+          <t>637720481</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1088938826</t>
+          <t>https://m.place.naver.com/place/637720481</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -1966,25 +1954,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>네일요정</t>
+          <t>페브네일</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>duddnd121@naver.com</t>
+          <t>yearning1128@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1375-8044</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 안연로 8 1층 미앤끼헤어네일</t>
+          <t>부산광역시 연제구 반송로 62-17 1층 페브네일</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/giggle_nailtip</t>
+          <t>http://www.instagram.com/feb_nail</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2019,13 +2011,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>230</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>6</v>
+        <v>242</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,17 +2026,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1208223075</t>
+          <t>1968946087</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1208223075</t>
+          <t>https://m.place.naver.com/place/1968946087</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2056,39 +2048,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>효리의빛나는네일</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>too1823@naver.com</t>
-        </is>
-      </c>
+          <t>포쉴리뷰티&amp;스킨&amp;바디</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1341-9746</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제대로 275 상가동 지1층 107호</t>
+          <t>부산광역시 연제구 과정로294번가길 20 1층 포쉴리뷰티</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://toss.place/_lb/TZUW7eqR3</t>
+          <t>https://www.instagram.com/poshly_beauty</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2104,7 +2088,7 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2113,13 +2097,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="Q18" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2112,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>2040725905</t>
+          <t>1813929104</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2040725905</t>
+          <t>https://m.place.naver.com/place/1813929104</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2150,29 +2134,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>마틸다네일</t>
+          <t>네시일분 예뻐지는시간</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>wngml2572@naver.com</t>
+          <t>alal7667@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1363-7291</t>
+          <t>0507-1335-9404</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로 18 2층</t>
+          <t>부산광역시 연제구 과정로343번길 22 더스타a동 101호 네시일분</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/stWnFTNg</t>
+          <t>https://www.instagram.com/nesiilbun_beauty</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2198,7 +2182,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2207,13 +2191,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="Q19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R19" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,17 +2206,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1247183274</t>
+          <t>1660019694</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1247183274</t>
+          <t>https://m.place.naver.com/place/1660019694</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2244,29 +2228,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>네일,도하</t>
+          <t>더네일</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nsj610@naver.com</t>
+          <t>thenail7282@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1498-5458</t>
+          <t>0507-1311-1145</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로11번길 114 1층 102호 네일,도하</t>
+          <t>부산광역시 연제구 거제대로178번길 55-1 더네일</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_doha_</t>
+          <t>http://www.instagram.com/the_nail120</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2301,13 +2285,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R20" t="n">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2316,17 +2300,17 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1673520422</t>
+          <t>1230694056</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1673520422</t>
+          <t>https://m.place.naver.com/place/1230694056</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2338,34 +2322,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nail빛</t>
+          <t>네일리크</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>theshiny_nail@naver.com</t>
+          <t>nailique25@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1322-9781</t>
+          <t>0507-1449-2433</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 80 연산동일동미라주 106동 1층상가 네일빛</t>
+          <t>부산광역시 연제구 월드컵대로79번길 50 1층</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_ybit</t>
+          <t>http://pf.kakao.com/_Vyesn</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2386,7 +2370,7 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2395,13 +2379,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="Q21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R21" t="n">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,17 +2394,17 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1478119147</t>
+          <t>1290184827</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1478119147</t>
+          <t>https://m.place.naver.com/place/1290184827</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2432,29 +2416,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>코코로네일</t>
+          <t>벨라티뷰티 부산시청점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>romina97@naver.com</t>
+          <t>mijooaa@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1316-7319</t>
+          <t>0507-1477-0829</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로114번길 4 1층 코코로네일</t>
+          <t>부산광역시 연제구 신촌로 20 2층</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/vellati_b?igsh=MWQ2NXlvN2J0Zmw2NQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2464,7 +2448,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2485,17 +2469,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R22" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,17 +2488,17 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1258381982</t>
+          <t>2002445034</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1258381982</t>
+          <t>https://m.place.naver.com/place/2002445034</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2526,29 +2510,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>오늘의네일</t>
+          <t>더미뉴네일</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>redcherry88@naver.com</t>
+          <t>mj_2023@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1398-3444</t>
+          <t>0507-1460-0699</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로 254 1층</t>
+          <t>부산광역시 연제구 연수로 173 1층</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>http://instagram.com/cny3444</t>
+          <t>https://www.instagram.com/theminew.nail</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2583,13 +2567,13 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>130</v>
+      </c>
+      <c r="Q23" t="n">
         <v>5</v>
       </c>
-      <c r="Q23" t="n">
-        <v>27</v>
-      </c>
       <c r="R23" t="n">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,17 +2582,17 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>1838257805</t>
+          <t>1260374485</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1838257805</t>
+          <t>https://m.place.naver.com/place/1260374485</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2620,29 +2604,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>벨라티뷰티 부산시청점</t>
+          <t>원더우먼 네일</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mijooaa@naver.com</t>
+          <t>sh88351@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0507-1477-0829</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신촌로 20 2층</t>
+          <t>부산광역시 연제구 월드컵대로 76 모티더베스트빌 상가 103호</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/vellati_b?igsh=MWQ2NXlvN2J0Zmw2NQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/wonder8686774</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2677,13 +2657,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="R24" t="n">
-        <v>89</v>
+        <v>25</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2672,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2002445034</t>
+          <t>1190599964</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2002445034</t>
+          <t>https://m.place.naver.com/place/1190599964</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2714,34 +2694,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>네일르누보</t>
+          <t>소르베네일 부산시청점</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ekgus618@naver.com</t>
+          <t>neulhappy_@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0507-1459-8386</t>
+          <t>0507-1487-4679</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로 7 132동 204호</t>
+          <t>부산광역시 연제구 중앙대로1038번길 40 근린생활시설 D동 2층 208호</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_renouveau_2?igsh=MW55NjlxOTE3dGUyaw==</t>
+          <t>https://pf.kakao.com/_xdHhHn</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2762,7 +2742,7 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2771,13 +2751,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>173</v>
+        <v>18</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2786,17 +2766,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1342130355</t>
+          <t>2032602450</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342130355</t>
+          <t>https://m.place.naver.com/place/2032602450</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2808,29 +2788,25 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>더킴스네일뷰티</t>
+          <t>네일이야기</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>rlawlgo85@naver.com</t>
+          <t>mimi7807@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0507-1420-5259</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 19 신종빌딩 5층</t>
+          <t>부산광역시 연제구 배산로23번길 4</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/thekims2012?igsh=Nmp3ZWN4NmRrYjA5&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/mimi7807</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2845,7 +2821,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2865,13 +2841,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>232</v>
+        <v>5</v>
       </c>
       <c r="Q26" t="n">
-        <v>958</v>
+        <v>21</v>
       </c>
       <c r="R26" t="n">
-        <v>1190</v>
+        <v>26</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2880,17 +2856,17 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>31098912</t>
+          <t>1983677901</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/31098912</t>
+          <t>https://m.place.naver.com/place/1983677901</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2902,34 +2878,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>라움네일</t>
+          <t>리앤뷰티네일</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>realbarbie77@naver.com</t>
+          <t>wnqkf517@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0507-1445-8116</t>
+          <t>0507-1341-3798</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로73번길 4 1층 라움네일</t>
+          <t>부산광역시 연제구 거제천로 105-1 3층 리앤뷰티네일</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_raum__nail?igsh=MThxa3BoYmF1cGR0YQ%3D%3D&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2939,7 +2915,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2959,13 +2935,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2974,17 +2950,17 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1012943186</t>
+          <t>1056219004</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1012943186</t>
+          <t>https://m.place.naver.com/place/1056219004</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2996,25 +2972,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>네일 더 예쁜</t>
+          <t>라움네일</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>dc2452@naver.com</t>
+          <t>imraina@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1445-8116</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로218번길 2 2층</t>
+          <t>부산광역시 연제구 월드컵대로73번길 4 1층 라움네일</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/_raum__nail?igsh=MThxa3BoYmF1cGR0YQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3024,7 +3004,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -3045,17 +3025,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>57</v>
+        <v>73</v>
       </c>
       <c r="Q28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3064,17 +3044,17 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>2054952880</t>
+          <t>1012943186</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2054952880</t>
+          <t>https://m.place.naver.com/place/1012943186</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3086,29 +3066,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>유니스네일뷰티</t>
+          <t>클래시네일</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>soyun4241@naver.com</t>
+          <t>classynail_@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0507-1382-4241</t>
+          <t>0507-1430-1890</t>
         </is>
       </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로230번길 61 1층 유니스네일뷰티</t>
+          <t>부산광역시 연제구 연제로 30 상가 203동 105호</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/artist_yunice</t>
+          <t>https://blog.naver.com/classynail_</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3123,7 +3103,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3143,13 +3123,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="Q29" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3158,17 +3138,17 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1725318910</t>
+          <t>1456426601</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1725318910</t>
+          <t>https://m.place.naver.com/place/1456426601</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3180,29 +3160,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>썬즈네일</t>
+          <t>네일르엔</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>suns-nail@naver.com</t>
+          <t>reruns_@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0507-1468-2628</t>
+          <t>0507-1357-6422</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로28번길 9 상가동 1층 209호 썬즈네일</t>
+          <t>부산광역시 연제구 월드컵대로 140 상진빌딩 2층</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sunsnail</t>
+          <t>https://www.instagram.com/nail_le.n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3228,7 +3208,7 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3237,13 +3217,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="Q30" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="R30" t="n">
-        <v>126</v>
+        <v>205</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3252,17 +3232,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1468663766</t>
+          <t>1665472449</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1468663766</t>
+          <t>https://m.place.naver.com/place/1665472449</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3274,29 +3254,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>루미가넷 네일존 사직</t>
+          <t>네일빨주노초파남보</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>webmore@naver.com</t>
+          <t>eunbyeol11@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>070-7012-9336</t>
+          <t>051-853-7795</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 종합운동장로 7 아시아드 홈플러스 지하1층 네일존</t>
+          <t>부산광역시 연제구 과정로344번길 19 1층</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/luv_rainbowww</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3306,7 +3286,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -3327,17 +3307,17 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3346,17 +3326,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1179495995</t>
+          <t>37033609</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1179495995</t>
+          <t>https://m.place.naver.com/place/37033609</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3368,29 +3348,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>페브네일</t>
+          <t>네일이나</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>yearning1128@naver.com</t>
+          <t>merryhunter@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1375-8044</t>
+          <t>0507-1323-8536</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 62-17 1층 페브네일</t>
+          <t>부산광역시 연제구 신금로 17-1 1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/feb_nail</t>
+          <t>https://www.instagram.com/nail_e.na?igsh=cnA0dTEwMTdjamE4</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3425,13 +3405,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>230</v>
+        <v>10</v>
       </c>
       <c r="Q32" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>242</v>
+        <v>10</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3440,17 +3420,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1968946087</t>
+          <t>2043892240</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1968946087</t>
+          <t>https://m.place.naver.com/place/2043892240</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3462,30 +3442,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>네일블리진</t>
+          <t>바비랑네일</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rkmgl2622@naver.com</t>
+          <t>9001177@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>051-867-9910</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1039-1 3층</t>
+          <t>부산광역시 연제구 중앙대로1039번길 15 . 1층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_YxbxmQT</t>
+          <t>https://www.instagram.com/babirang_</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3506,7 +3490,7 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3515,13 +3499,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="Q33" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="R33" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3530,17 +3514,17 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1051433565</t>
+          <t>950132087</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1051433565</t>
+          <t>https://m.place.naver.com/place/950132087</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3552,29 +3536,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>명월네일샵</t>
+          <t>라보니 네일</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>leekatanail@naver.com</t>
+          <t>eunberry-@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0507-1461-1196</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 246</t>
+          <t>부산광역시 연제구 거제천로87번길 30 101동 1층 106호</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/leekatanail</t>
+          <t>https://www.instagram.com/nail_rabboni</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3589,7 +3569,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3609,13 +3589,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3624,17 +3604,17 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1031904006</t>
+          <t>1232347337</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1031904006</t>
+          <t>https://m.place.naver.com/place/1232347337</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3646,34 +3626,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>뷰티진담</t>
+          <t>이유네일 부산연산점</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>daily_luhee@naver.com</t>
+          <t>todnfksp1@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1321-5412</t>
+          <t>0507-1357-5036</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1043번길 34 시청역 sk뷰 2층 206호</t>
+          <t>부산광역시 연제구 중앙대로 1130 2층 206호</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://open.kakao.com/me/beauty_jindam</t>
+          <t>https://www.instagram.com/leeyu_nail_</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3694,7 +3674,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3703,13 +3683,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>42</v>
+        <v>491</v>
       </c>
       <c r="Q35" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="R35" t="n">
-        <v>60</v>
+        <v>536</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3718,17 +3698,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1992381741</t>
+          <t>1682866660</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1992381741</t>
+          <t>https://m.place.naver.com/place/1682866660</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3740,29 +3720,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>히니네일 부산연산점</t>
+          <t>로제이네일</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>yuu_ja@naver.com</t>
+          <t>permisi@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0507-1391-1454</t>
+          <t>0507-1340-1354</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1130 연산동 SK VIE W 2단지 1층 114호</t>
+          <t>부산광역시 연제구 과정로191번다길 61 로제이 네일</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/heeni_nail</t>
+          <t>https://www.instagram.com/ro.j_nail?igsh=MWU4ZXBiczVvaTdlaQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3797,13 +3777,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>136</v>
+        <v>1</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3812,17 +3792,17 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1114751434</t>
+          <t>1088938826</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1114751434</t>
+          <t>https://m.place.naver.com/place/1088938826</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3834,29 +3814,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>럭스네일팁</t>
+          <t>마이네일</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nailluxe@naver.com</t>
+          <t>mynail_busan@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1432-0046</t>
+          <t>051-851-2458</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제시장로 23</t>
+          <t>부산광역시 연제구 반송로 40 e편한세상 연산 더퍼스트상가 1층</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>http://www.luxenailtip.co.kr/</t>
+          <t>https://blog.naver.com/mynail_busan</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -3871,7 +3851,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3887,17 +3867,17 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>290</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3906,17 +3886,17 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>57487992</t>
+          <t>36234466</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/57487992</t>
+          <t>https://m.place.naver.com/place/36234466</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3928,29 +3908,29 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>네일콕</t>
+          <t>모브네일 연산본점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>zwonii@naver.com</t>
+          <t>rkfla2321@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0507-1461-8217</t>
+          <t>0507-1390-9765</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1124번길 20 2층 내부</t>
+          <t>부산광역시 연제구 고분로 38 1층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/spc5ofyg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3960,7 +3940,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3976,22 +3956,22 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="Q38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -4000,17 +3980,17 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>2022960036</t>
+          <t>2006582698</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2022960036</t>
+          <t>https://m.place.naver.com/place/2006582698</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4022,29 +4002,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아이앤아이 속눈썹 네일 부산연산점</t>
+          <t>네일스튜디오 바이 민</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>eyeneye_nailroom@naver.com</t>
+          <t>seongaya@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1307-7896</t>
+          <t>051-939-8726</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 144 a동 1층 아이앤아이</t>
+          <t>부산광역시 연제구 안연로 33 상가 A동 110호</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bty.x0725</t>
+          <t>https://blog.naver.com/seongaya</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4059,7 +4039,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4079,13 +4059,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="Q39" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>166</v>
+        <v>7</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4094,17 +4074,17 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>1303501565</t>
+          <t>1709352377</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1303501565</t>
+          <t>https://m.place.naver.com/place/1709352377</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4116,29 +4096,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>티우네일</t>
+          <t>네일앤미</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>hdaek10@naver.com</t>
+          <t>nkm1004@naver.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0507-1361-8683</t>
+          <t>0507-1329-5080</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로343번길 22 B동 101호</t>
+          <t>부산광역시 연제구 월드컵대로 282 청목파르테논705호</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/t.woo_nail</t>
+          <t>https://smartstore.naver.com/nailnmi</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4173,13 +4153,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>128</v>
+        <v>55</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="R40" t="n">
-        <v>144</v>
+        <v>103</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4188,17 +4168,17 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1428190568</t>
+          <t>121674192</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1428190568</t>
+          <t>https://m.place.naver.com/place/121674192</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4210,29 +4190,29 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>네일커브</t>
+          <t>네일 더 드리밍 연산시청점</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>nailcurve@naver.com</t>
+          <t>ssongs_yummy@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0507-1363-0436</t>
+          <t>0507-1347-4595</t>
         </is>
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로343번길 9 1층 네일커브</t>
+          <t>부산광역시 연제구 중앙천로 8 1층 네일 더 드리밍 연산시청점</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail__cv</t>
+          <t>https://www.instagram.com/nail_the.dreaming</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4267,13 +4247,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>95</v>
+        <v>238</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R41" t="n">
-        <v>109</v>
+        <v>256</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4282,17 +4262,17 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>1692126809</t>
+          <t>1491294937</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1692126809</t>
+          <t>https://m.place.naver.com/place/1491294937</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4304,29 +4284,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>꼭대기네일</t>
+          <t>더킴스네일뷰티</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>foresten@naver.com</t>
+          <t>rlawlgo85@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1340-4140</t>
+          <t>0507-1420-5259</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 화지로 95 거제청구하이츠아파트 상가동 1층</t>
+          <t>부산광역시 연제구 반송로 19 신종빌딩 5층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/thekims2012?igsh=Nmp3ZWN4NmRrYjA5&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4336,7 +4316,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4357,17 +4337,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>22</v>
+        <v>232</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>958</v>
       </c>
       <c r="R42" t="n">
-        <v>22</v>
+        <v>1190</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4376,17 +4356,17 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1056754569</t>
+          <t>31098912</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1056754569</t>
+          <t>https://m.place.naver.com/place/31098912</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4398,30 +4378,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>오브네일</t>
+          <t>네일 오 그레이</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ofrang@naver.com</t>
+          <t>dongju5104@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>0507-1469-0621</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로4번길 5 1층 102호</t>
+          <t>부산광역시 연제구 신금로17번길 46 1층</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_ove.nail?igsh=aWdkcjE3bDZiaHFi</t>
+          <t>http://pf.kakao.com/_Sdpxmxj</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4442,7 +4426,7 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4451,13 +4435,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>79</v>
+        <v>358</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4466,17 +4450,17 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1870621262</t>
+          <t>1842181845</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1870621262</t>
+          <t>https://m.place.naver.com/place/1842181845</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4488,29 +4472,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>레푸스 연산시청점</t>
+          <t>썬즈네일</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>refuss_@naver.com</t>
+          <t>suns-nail@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0507-1443-6687</t>
+          <t>0507-1468-2628</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 시청로 26-1 2층 (베스킨라빈스건물)</t>
+          <t>부산광역시 연제구 아시아드대로28번길 9 상가동 1층 209호 썬즈네일</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/refuss_yeonsan</t>
+          <t>https://www.instagram.com/sunsnail</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4545,13 +4529,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1481</v>
+        <v>115</v>
       </c>
       <c r="Q44" t="n">
-        <v>432</v>
+        <v>11</v>
       </c>
       <c r="R44" t="n">
-        <v>1913</v>
+        <v>126</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4560,17 +4544,17 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1842243644</t>
+          <t>1468663766</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1842243644</t>
+          <t>https://m.place.naver.com/place/1468663766</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4582,25 +4566,29 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>뷰티투미</t>
+          <t>제니엘뷰티</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>beauty_to_mi@naver.com</t>
+          <t>jennyelbeauty@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1328-8789</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로114번길 13 2층 뷰티투미</t>
+          <t>부산광역시 연제구 중앙대로 1077 메디컬시티 12층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/beauty_to_mi</t>
+          <t>https://blog.naver.com/jennyelbeauty</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4635,13 +4623,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="Q45" t="n">
-        <v>29</v>
+        <v>207</v>
       </c>
       <c r="R45" t="n">
-        <v>46</v>
+        <v>217</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4650,17 +4638,17 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1065937655</t>
+          <t>1580331994</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1065937655</t>
+          <t>https://m.place.naver.com/place/1580331994</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4672,29 +4660,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>네일시스</t>
+          <t>연산동_네일,더빛날</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>mjmj012@naver.com</t>
+          <t>potato00214@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1409-0104</t>
+          <t>0507-1432-1799</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로124번길 48 1층 101호</t>
+          <t>부산광역시 연제구 중앙대로1076번길 30 1층</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/__nailsis</t>
+          <t>https://www.instagram.com/nail_thevitnal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4729,13 +4717,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R46" t="n">
-        <v>34</v>
+        <v>155</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4744,17 +4732,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1498091323</t>
+          <t>1424947348</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1498091323</t>
+          <t>https://m.place.naver.com/place/1424947348</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4754,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>라보니 네일</t>
+          <t>네일맑음</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>eunberry-@naver.com</t>
+          <t>s1514@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -4779,12 +4767,12 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로87번길 30 101동 1층 106호</t>
+          <t>부산광역시 연제구 연수로 204-1 1층 네일맑음</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_rabboni</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4794,7 +4782,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4815,17 +4803,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="R47" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4834,17 +4822,17 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1232347337</t>
+          <t>1944625741</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1232347337</t>
+          <t>https://m.place.naver.com/place/1944625741</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4856,29 +4844,29 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>딴네일</t>
+          <t>효리의빛나는네일</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nobleliz_@naver.com</t>
+          <t>too1823@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1413-7542</t>
+          <t>0507-1341-9746</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1134번길 51 1층 딴네일</t>
+          <t>부산광역시 연제구 거제대로 275 상가동 지1층 107호</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>http://instagram.com/ddan_nail7542</t>
+          <t>https://www.instagram.com/hyori_nail</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4904,7 +4892,7 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4913,13 +4901,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="Q48" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="R48" t="n">
-        <v>30</v>
+        <v>179</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4928,17 +4916,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1750949440</t>
+          <t>2040725905</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1750949440</t>
+          <t>https://m.place.naver.com/place/2040725905</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4950,34 +4938,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>네일룸</t>
+          <t>네일블리진</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>gumi_nailroom@naver.com</t>
+          <t>rkmgl2622@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>0507-1365-2725</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 좌수영로 225 S101동 1층 B205호 네일룸</t>
+          <t>부산광역시 연제구 중앙대로 1039-1 3층</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailroom_busan</t>
+          <t>http://pf.kakao.com/_YxbxmQT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -5007,13 +4991,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="R49" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5022,17 +5006,17 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1755198272</t>
+          <t>1051433565</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1755198272</t>
+          <t>https://m.place.naver.com/place/1051433565</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5044,29 +5028,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>블랑코뷰티</t>
+          <t>라로제네일</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>estheticianjoy@naver.com</t>
+          <t>brushlounge@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0507-1353-4174</t>
+          <t>0507-1343-8177</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 166 1층 블랑코뷰티</t>
+          <t>부산광역시 연제구 신금로 18 2층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sOUjZO1c</t>
+          <t>https://open.kakao.com/o/sYvUmDpi</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5101,13 +5085,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5116,17 +5100,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1657028472</t>
+          <t>2039316974</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1657028472</t>
+          <t>https://m.place.naver.com/place/2039316974</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5138,34 +5122,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>채움네일</t>
+          <t>노니네일</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>rhdwnsla5656@naver.com</t>
+          <t>siunim@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0507-1340-9768</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 7 2층</t>
+          <t>부산광역시 연제구 월드컵대로73번길 82 풀잎하우스빌 1층 101호</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/yoming22</t>
+          <t>http://pf.kakao.com/_Wgxnzxj</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5186,7 +5166,7 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5195,13 +5175,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5210,17 +5190,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1801826590</t>
+          <t>1561653317</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1801826590</t>
+          <t>https://m.place.naver.com/place/1561653317</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5232,29 +5212,29 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>라루즈살롱</t>
+          <t>코코로네일</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>boram1646@naver.com</t>
+          <t>romina97@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0507-1388-3851</t>
+          <t>0507-1316-7319</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1130 SK뷰 2단지 2층 201호</t>
+          <t>부산광역시 연제구 과정로114번길 4 1층 코코로네일</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/laluz.salon/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5264,7 +5244,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -5285,17 +5265,17 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>374</v>
+        <v>63</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>377</v>
+        <v>63</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5304,17 +5284,17 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1358321177</t>
+          <t>1258381982</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1358321177</t>
+          <t>https://m.place.naver.com/place/1258381982</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5326,25 +5306,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>네일이야기</t>
+          <t>ONE네일</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>mimi7807@naver.com</t>
+          <t>garam_soo@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0507-1349-6159</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 배산로23번길 4</t>
+          <t>부산광역시 연제구 중앙대로 1049 3층</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mimi7807</t>
+          <t>https://instagram.com/onenail_onenail?igshid=ZDdkNTZiNTM=</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5359,7 +5343,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5379,13 +5363,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="Q53" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5394,17 +5378,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1983677901</t>
+          <t>1153323846</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1983677901</t>
+          <t>https://m.place.naver.com/place/1153323846</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5416,29 +5400,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>네일 드네쥬</t>
+          <t>유화네일 부산시청점</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>denejue@naver.com</t>
+          <t>zkscy711@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1312-5886</t>
+          <t>0507-1427-6564</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 토곡로 37 1층</t>
+          <t>부산광역시 연제구 중앙천로 81-17 1층 102호</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_denejue?igsh=dHRxMHR2aHJidjg0&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/yuhwa__nail</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5473,13 +5457,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="Q54" t="n">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>167</v>
+        <v>37</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5488,17 +5472,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1892993746</t>
+          <t>1340666587</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1892993746</t>
+          <t>https://m.place.naver.com/place/1340666587</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5510,29 +5494,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>마이네일</t>
+          <t>네일,도하</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>mynail_busan@naver.com</t>
+          <t>nsj610@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>051-851-2458</t>
+          <t>0507-1498-5458</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 40 e편한세상 연산 더퍼스트상가 1층</t>
+          <t>부산광역시 연제구 연수로11번길 114 1층 102호 네일,도하</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mynail_busan</t>
+          <t>https://www.instagram.com/nail_doha_</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5547,7 +5531,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5567,13 +5551,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>135</v>
+        <v>20</v>
       </c>
       <c r="Q55" t="n">
-        <v>155</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5582,17 +5566,17 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>36234466</t>
+          <t>1673520422</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36234466</t>
+          <t>https://m.place.naver.com/place/1673520422</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5604,29 +5588,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>썸네일</t>
+          <t>네일그리다</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>taiji0929@naver.com</t>
+          <t>duz8107@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>051-852-4153</t>
+          <t>0507-1321-5388</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로 16 썸네일</t>
+          <t>부산광역시 연제구 반송로 68 네일그리다</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/taiji0929</t>
+          <t>https://www.instagram.com/nailgrida_jh</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5661,13 +5645,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>43</v>
+        <v>229</v>
       </c>
       <c r="Q56" t="n">
-        <v>274</v>
+        <v>60</v>
       </c>
       <c r="R56" t="n">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5676,17 +5660,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>35243970</t>
+          <t>38404003</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35243970</t>
+          <t>https://m.place.naver.com/place/38404003</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5698,25 +5682,29 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>네일맑음</t>
+          <t>라르네일</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>s1514@naver.com</t>
+          <t>dlqnsr_@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>0507-1375-1612</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 204-1 1층 네일맑음</t>
+          <t>부산광역시 연제구 신금로23번길 56 1층 라르네일</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nail_lart_</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5726,7 +5714,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -5747,17 +5735,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1</v>
+        <v>253</v>
       </c>
       <c r="Q57" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R57" t="n">
-        <v>13</v>
+        <v>261</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5766,17 +5754,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1944625741</t>
+          <t>1477228054</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944625741</t>
+          <t>https://m.place.naver.com/place/1477228054</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5788,29 +5776,25 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>라르네일</t>
+          <t>오브네일</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>dlqnsr_@naver.com</t>
+          <t>capcue@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>0507-1375-1612</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로23번길 56 1층 라르네일</t>
+          <t>부산광역시 연제구 중앙천로4번길 5 1층 102호</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_lart_</t>
+          <t>https://www.instagram.com/_ove.nail?igsh=aWdkcjE3bDZiaHFi</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5845,13 +5829,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>253</v>
+        <v>76</v>
       </c>
       <c r="Q58" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>261</v>
+        <v>79</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5860,17 +5844,17 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1477228054</t>
+          <t>1870621262</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1477228054</t>
+          <t>https://m.place.naver.com/place/1870621262</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5882,29 +5866,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>가온네일</t>
+          <t>벨루아뷰티</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>leedmswh8898@naver.com</t>
+          <t>sh26888@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>0507-1345-8019</t>
-        </is>
-      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 82 삼정그린코아포레스트 상가동 210호</t>
+          <t>부산광역시 연제구 쌍미천로 147 3층</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gaonnail_/</t>
+          <t>https://www.instagram.com/bellua_beauty?igsh=MWltZ2hrbWZpYzAxdw%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5939,13 +5919,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>191</v>
+        <v>46</v>
       </c>
       <c r="Q59" t="n">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="R59" t="n">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5954,17 +5934,17 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>1960748053</t>
+          <t>2086054910</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1960748053</t>
+          <t>https://m.place.naver.com/place/2086054910</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -5976,29 +5956,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>신지네일&amp;메이크업 연산동점</t>
+          <t>엘유네일</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>springonion_eggs@naver.com</t>
+          <t>kikanaa@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0507-1309-9627</t>
+          <t>0507-1306-9767</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1124번길 15 1층상가</t>
+          <t>부산광역시 연제구 중앙대로1075번길 58 1층 엘유네일</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/shinzinail/</t>
+          <t>https://www.instagram.com/lu_nail___</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6033,13 +6013,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>181</v>
+        <v>43</v>
       </c>
       <c r="Q60" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>475</v>
+        <v>43</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -6048,17 +6028,17 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>1776187392</t>
+          <t>2036505455</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1776187392</t>
+          <t>https://m.place.naver.com/place/2036505455</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6070,25 +6050,29 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>노니네일</t>
+          <t>뷰티진담</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>siunim@naver.com</t>
+          <t>daily_luhee@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0507-1321-5412</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로73번길 82 풀잎하우스빌 1층 101호</t>
+          <t>부산광역시 연제구 중앙대로1043번길 34 시청역 sk뷰 2층 206호</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Wgxnzxj</t>
+          <t>http://open.kakao.com/me/beauty_jindam</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6123,13 +6107,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R61" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6138,17 +6122,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1561653317</t>
+          <t>1992381741</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1561653317</t>
+          <t>https://m.place.naver.com/place/1992381741</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6160,34 +6144,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>네일앤미</t>
+          <t>럭스네일팁</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>nkm1004@naver.com</t>
+          <t>nailluxe@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1329-5080</t>
+          <t>0507-1432-0046</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 282 청목파르테논705호</t>
+          <t>부산광역시 연제구 거제시장로 23</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/nailnmi</t>
+          <t>http://www.luxenailtip.co.kr/</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -6213,17 +6197,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6232,17 +6216,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>121674192</t>
+          <t>57487992</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/121674192</t>
+          <t>https://m.place.naver.com/place/57487992</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6254,29 +6238,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>라온네일</t>
+          <t>네일르누보</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>yutin60537@naver.com</t>
+          <t>ekgus618@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1364-1656</t>
+          <t>0507-1459-8386</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로32번길 23 1층</t>
+          <t>부산광역시 연제구 아시아드대로 7 132동 204호</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>http://instagram.com/la_on_nail</t>
+          <t>https://www.instagram.com/nail_renouveau_2?igsh=MW55NjlxOTE3dGUyaw==</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6311,13 +6295,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="Q63" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="R63" t="n">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6326,17 +6310,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1100502822</t>
+          <t>1342130355</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1100502822</t>
+          <t>https://m.place.naver.com/place/1342130355</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6348,29 +6332,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>클래시네일</t>
+          <t>마틸다네일</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>classynail_@naver.com</t>
+          <t>wngml2572@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0507-1430-1890</t>
+          <t>0507-1363-7291</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연제로 30 상가 203동 105호</t>
+          <t>부산광역시 연제구 신금로 18 2층</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/classynail_</t>
+          <t>https://open.kakao.com/o/stWnFTNg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6385,7 +6369,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6396,7 +6380,7 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6405,13 +6389,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="Q64" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="R64" t="n">
-        <v>166</v>
+        <v>42</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6420,17 +6404,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1456426601</t>
+          <t>1247183274</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1456426601</t>
+          <t>https://m.place.naver.com/place/1247183274</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6442,29 +6426,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>네일포유</t>
+          <t>네일,그날</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>nail_for_u@naver.com</t>
+          <t>nahe0904@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0507-1480-6706</t>
+          <t>0507-1476-4141</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 금용로 5 1층</t>
+          <t>부산광역시 연제구 연수로 125-1 2층</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_for_you_6694</t>
+          <t>http://instagram.com/nail_theday.__</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6499,13 +6483,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="Q65" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R65" t="n">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6514,17 +6498,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1173016573</t>
+          <t>1061426000</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1173016573</t>
+          <t>https://m.place.naver.com/place/1061426000</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6536,29 +6520,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>제니엘뷰티</t>
+          <t>티우네일</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jennyelbeauty@naver.com</t>
+          <t>hdaek10@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1328-8789</t>
+          <t>0507-1361-8683</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1077 메디컬시티 12층</t>
+          <t>부산광역시 연제구 과정로343번길 22 B동 101호</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jennyelbeauty</t>
+          <t>https://www.instagram.com/t.woo_nail</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6573,7 +6557,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6593,13 +6577,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>10</v>
+        <v>128</v>
       </c>
       <c r="Q66" t="n">
-        <v>207</v>
+        <v>16</v>
       </c>
       <c r="R66" t="n">
-        <v>217</v>
+        <v>144</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6608,17 +6592,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1580331994</t>
+          <t>1428190568</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1580331994</t>
+          <t>https://m.place.naver.com/place/1428190568</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6630,29 +6614,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>네일커밍</t>
+          <t>2월11일네일</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>coming230201@naver.com</t>
+          <t>designmania@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0507-1327-0497</t>
+          <t>0507-1329-6882</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로208번길 16</t>
+          <t>부산광역시 연제구 중앙대로 1063 5층</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/coming230201</t>
+          <t>http://www.instagram.com/211_nail</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6667,7 +6651,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6687,13 +6671,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>160</v>
+        <v>211</v>
       </c>
       <c r="Q67" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="R67" t="n">
-        <v>184</v>
+        <v>269</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6702,17 +6686,17 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>1185455703</t>
+          <t>1816506274</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1185455703</t>
+          <t>https://m.place.naver.com/place/1816506274</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6724,25 +6708,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>벨루아뷰티</t>
+          <t>네일콕</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sh26888@naver.com</t>
+          <t>zwonii@naver.com</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>0507-1461-8217</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 쌍미천로 147 3층</t>
+          <t>부산광역시 연제구 중앙대로1124번길 20 2층 내부</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bellua_beauty?igsh=MWltZ2hrbWZpYzAxdw%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6752,7 +6740,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6773,17 +6761,17 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P68" t="n">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="Q68" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R68" t="n">
-        <v>63</v>
+        <v>16</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6792,17 +6780,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>2086054910</t>
+          <t>2022960036</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086054910</t>
+          <t>https://m.place.naver.com/place/2022960036</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6814,29 +6802,29 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>네일,그날</t>
+          <t>네일 드네쥬</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>nahe0904@naver.com</t>
+          <t>denejue@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0507-1476-4141</t>
+          <t>0507-1312-5886</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 125-1 2층</t>
+          <t>부산광역시 연제구 토곡로 37 1층</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_theday.__</t>
+          <t>https://www.instagram.com/nail_denejue?igsh=dHRxMHR2aHJidjg0&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6871,13 +6859,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="Q69" t="n">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="R69" t="n">
-        <v>109</v>
+        <v>167</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6886,17 +6874,17 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1061426000</t>
+          <t>1892993746</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1061426000</t>
+          <t>https://m.place.naver.com/place/1892993746</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -6908,29 +6896,29 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>이유네일 부산연산점</t>
+          <t>네일커밍</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>todnfksp1@naver.com</t>
+          <t>coming230201@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0507-1357-5036</t>
+          <t>0507-1327-0497</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1130 2층 206호</t>
+          <t>부산광역시 연제구 과정로208번길 16</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/leeyu_nail_</t>
+          <t>https://blog.naver.com/coming230201</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6945,7 +6933,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6965,13 +6953,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>491</v>
+        <v>160</v>
       </c>
       <c r="Q70" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="R70" t="n">
-        <v>536</v>
+        <v>184</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6980,17 +6968,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>1682866660</t>
+          <t>1185455703</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1682866660</t>
+          <t>https://m.place.naver.com/place/1185455703</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7002,29 +6990,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>보니또네일</t>
+          <t>딴네일</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ourcutelove@naver.com</t>
+          <t>nobleliz_@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0507-1479-7034</t>
+          <t>0507-1413-7542</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로 200 상가동 107호</t>
+          <t>부산광역시 연제구 중앙대로1134번길 51 1층 딴네일</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/bonitto__nail</t>
+          <t>http://instagram.com/ddan_nail7542</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7059,13 +7047,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="Q71" t="n">
         <v>3</v>
       </c>
       <c r="R71" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7074,17 +7062,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>1222997854</t>
+          <t>1750949440</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1222997854</t>
+          <t>https://m.place.naver.com/place/1750949440</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7096,29 +7084,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>코코네일</t>
+          <t>JM NAIL</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>jjuahlee@naver.com</t>
+          <t>qkrwjddms105@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>0507-1305-1030</t>
-        </is>
-      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 쌍미천로151번길 17</t>
+          <t>부산광역시 연제구 거제천로 258 연산해수피아 2층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>http://instagram.com/coconail_mj</t>
+          <t>https://www.instagram.com/jmnail0104</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7153,13 +7137,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="R72" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7168,17 +7152,17 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1043623932</t>
+          <t>1875116182</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043623932</t>
+          <t>https://m.place.naver.com/place/1875116182</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7190,29 +7174,29 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>오드레 네일</t>
+          <t>에스네일</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>seunjeung@naver.com</t>
+          <t>7gonggu@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1436-2772</t>
+          <t>0507-1303-4143</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로22번길 36 401동 103일부호</t>
+          <t>부산광역시 연제구 거제천로 258 연산해수피아 1층 105호</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/odrenail</t>
+          <t>https://blog.naver.com/7gonggu</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7227,7 +7211,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7238,7 +7222,7 @@
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7247,13 +7231,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>92</v>
+        <v>5</v>
       </c>
       <c r="Q73" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R73" t="n">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7262,17 +7246,17 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1326125631</t>
+          <t>1772096643</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1326125631</t>
+          <t>https://m.place.naver.com/place/1772096643</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7284,29 +7268,29 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>더혜뷰티 연산양정점</t>
+          <t>오드레 네일</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>seoin1999@naver.com</t>
+          <t>seunjeung@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0507-1471-0417</t>
+          <t>0507-1436-2772</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로87번길 3 3층</t>
+          <t>부산광역시 연제구 아시아드대로22번길 36 401동 103일부호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>http://instagram.com/the_hye_beauty</t>
+          <t>https://www.instagram.com/odrenail</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7332,7 +7316,7 @@
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7341,13 +7325,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>488</v>
+        <v>92</v>
       </c>
       <c r="Q74" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>513</v>
+        <v>95</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7356,17 +7340,17 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1695025021</t>
+          <t>1326125631</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1695025021</t>
+          <t>https://m.place.naver.com/place/1326125631</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7378,29 +7362,29 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>네일바</t>
+          <t>라루즈살롱</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>rosamatt@naver.com</t>
+          <t>boram1646@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>051-758-3963</t>
+          <t>0507-1388-3851</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로 80 1층</t>
+          <t>부산광역시 연제구 중앙대로 1130 SK뷰 2단지 2층 201호</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_bar._</t>
+          <t>https://www.instagram.com/laluz.salon/</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7435,13 +7419,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>57</v>
+        <v>374</v>
       </c>
       <c r="Q75" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="R75" t="n">
-        <v>121</v>
+        <v>377</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7450,17 +7434,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>32333430</t>
+          <t>1358321177</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/32333430</t>
+          <t>https://m.place.naver.com/place/1358321177</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7472,29 +7456,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>모브네일 연산본점</t>
+          <t>하정수네일</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>rkfla2321@naver.com</t>
+          <t>0hyeah6@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0507-1390-9765</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 고분로 38 1층</t>
+          <t>부산광역시 연제구 종합운동장로12번길 34</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/spc5ofyg</t>
+          <t>http://instagram.com/hjsnail</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7520,7 +7500,7 @@
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7529,13 +7509,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="Q76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -7544,17 +7524,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>2006582698</t>
+          <t>1060527554</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2006582698</t>
+          <t>https://m.place.naver.com/place/1060527554</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7566,39 +7546,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>온 네일</t>
+          <t>하루네일</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>guswnwnwn@naver.com</t>
+          <t>luv744@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0507-1446-3360</t>
+          <t>051-868-7333</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 시청로 12 더샵씨티애비뉴2차 상가 2층215호</t>
+          <t>부산광역시 연제구 거제천로255번가길 31 1층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://booking.naver.com/booking/13/bizes/526220</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -7619,17 +7599,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>36</v>
+        <v>137</v>
       </c>
       <c r="Q77" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="R77" t="n">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7638,17 +7618,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>189950209</t>
+          <t>1884949089</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/189950209</t>
+          <t>https://m.place.naver.com/place/1884949089</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7660,25 +7640,29 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>네일가예쁨</t>
+          <t>네일룸</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>narea7909@naver.com</t>
+          <t>ju8747@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>0507-1365-2725</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 233 주상가동 103-1호</t>
+          <t>부산광역시 연제구 좌수영로 225 S101동 1층 B205호 네일룸</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/nail_gayeppeum</t>
+          <t>https://www.instagram.com/nailroom_busan</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7704,7 +7688,7 @@
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7713,13 +7697,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="Q78" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7728,17 +7712,17 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>1192185627</t>
+          <t>1755198272</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1192185627</t>
+          <t>https://m.place.naver.com/place/1755198272</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7750,25 +7734,29 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>원더우먼 네일</t>
+          <t>네일바</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>sh88351@naver.com</t>
+          <t>rosamatt@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>051-758-3963</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 76 모티더베스트빌 상가 103호</t>
+          <t>부산광역시 연제구 과정로 80 1층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wonder8686774</t>
+          <t>http://instagram.com/nail_bar._</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7803,13 +7791,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="Q79" t="n">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="R79" t="n">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7818,17 +7806,17 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1190599964</t>
+          <t>32333430</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1190599964</t>
+          <t>https://m.place.naver.com/place/32333430</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7840,29 +7828,29 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>리본네일 부산시청점</t>
+          <t>Nail빛</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>girljakpoom@naver.com</t>
+          <t>theshiny_nail@naver.com</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1442-5066</t>
+          <t>0507-1322-9781</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1043번길 56 2층 리본네일 부산시청점</t>
+          <t>부산광역시 연제구 반송로 80 연산동일동미라주 106동 1층상가 네일빛</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/girljakpoom</t>
+          <t>http://instagram.com/nail_ybit</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7877,7 +7865,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -7897,13 +7885,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>141</v>
+        <v>300</v>
       </c>
       <c r="Q80" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="R80" t="n">
-        <v>150</v>
+        <v>328</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7912,17 +7900,17 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1260057809</t>
+          <t>1478119147</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260057809</t>
+          <t>https://m.place.naver.com/place/1478119147</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -7934,29 +7922,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>영네일</t>
+          <t>투에이치 뷰티</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>cy2403@naver.com</t>
+          <t>jieun961216@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>051-504-0506</t>
+          <t>0507-1391-0868</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로 95</t>
+          <t>부산광역시 연제구 신촌로 2 5층</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sZa5dynf</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7966,7 +7954,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7982,22 +7970,22 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="Q81" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="R81" t="n">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8006,17 +7994,17 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1168856867</t>
+          <t>1263305975</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1168856867</t>
+          <t>https://m.place.naver.com/place/1263305975</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8028,29 +8016,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>패디당</t>
+          <t>네일오예</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>pedidang@naver.com</t>
+          <t>efjekkk0888@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1302-3954</t>
+          <t>0507-1424-0360</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 82 삼정그린코아 포레스트 상가동 2층 211호</t>
+          <t>부산광역시 연제구 해맞이로67번길 23 102호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/pedi._.dang</t>
+          <t>https://www.instagram.com/nail_o.yeah?igsh=MTBrcDN2OHM5djY1cQ%3D%3D&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8085,13 +8073,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2</v>
+        <v>130</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R82" t="n">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8100,17 +8088,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2026492166</t>
+          <t>2070499527</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2026492166</t>
+          <t>https://m.place.naver.com/place/2070499527</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8122,25 +8110,29 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>하정수네일</t>
+          <t>뷰티더무드네일</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>0hyeah6@naver.com</t>
+          <t>hkj7713@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>0507-1438-2849</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 종합운동장로12번길 34</t>
+          <t>부산광역시 연제구 중앙대로1043번길 12 2층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>http://instagram.com/hjsnail</t>
+          <t>https://open.kakao.com/o/sgAjvNkg</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -8166,7 +8158,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8175,13 +8167,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="Q83" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="R83" t="n">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8190,17 +8182,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1060527554</t>
+          <t>1636008279</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060527554</t>
+          <t>https://m.place.naver.com/place/1636008279</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8212,12 +8204,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>바이요니네일</t>
+          <t>샬롬 네일</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>kitty_log@naver.com</t>
+          <t>aksrn1004@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -8225,12 +8217,12 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로 77-2 1층</t>
+          <t>부산광역시 연제구 토곡로 21</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>http://instagram.com/byyoni__nail</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8240,7 +8232,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8261,17 +8253,17 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P84" t="n">
-        <v>460</v>
+        <v>8</v>
       </c>
       <c r="Q84" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="R84" t="n">
-        <v>467</v>
+        <v>10</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8280,17 +8272,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>1418772825</t>
+          <t>1009508663</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1418772825</t>
+          <t>https://m.place.naver.com/place/1009508663</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8302,20 +8294,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>네일언니 by JU</t>
+          <t>영네일</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>amelie1223@naver.com</t>
+          <t>cy2403@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>051-504-0506</t>
+        </is>
+      </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 221-7</t>
+          <t>부산광역시 연제구 아시아드대로 95</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8355,13 +8351,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q85" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R85" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8370,17 +8366,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>637720481</t>
+          <t>1168856867</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/637720481</t>
+          <t>https://m.place.naver.com/place/1168856867</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8392,39 +8388,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>네일 오 그레이</t>
+          <t>미소네일</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ururu007@naver.com</t>
+          <t>rw0116@naver.com</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0507-1469-0621</t>
+          <t>0507-1388-4488</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로17번길 46 1층</t>
+          <t>부산광역시 연제구 신촌로 50 1층</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Sdpxmxj</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -8440,22 +8436,22 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -8464,17 +8460,17 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>1842181845</t>
+          <t>2008655896</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1842181845</t>
+          <t>https://m.place.naver.com/place/2008655896</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8486,29 +8482,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>랑뷰티</t>
+          <t>네일예쁨</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>bbakggu0723@naver.com</t>
+          <t>maeilyepboom@naver.com</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0507-1490-3542</t>
+          <t>0507-1463-5608</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로255번길 48 1층</t>
+          <t>부산광역시 연제구 연제로 21 힐스테이트상가 2층 203호(홍익노무법인건물)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/adst8888</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -8518,7 +8514,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8539,17 +8535,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -8558,17 +8554,17 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>2088276975</t>
+          <t>1462213612</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2088276975</t>
+          <t>https://m.place.naver.com/place/1462213612</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8580,29 +8576,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>엔피케어 부산연산점</t>
+          <t>츄제이네일 부산연산점</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>np_care@naver.com</t>
+          <t>qhdwkzz@naver.com</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>0507-1449-2096</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1114 4층</t>
+          <t>부산광역시 연제구 중앙대로 1130 SK뷰 2단지 2층 216호 츄제이네일</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NPCARE_</t>
+          <t>https://www.instagram.com/chuuj_nail</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -8617,7 +8609,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -8637,13 +8629,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>579</v>
+        <v>227</v>
       </c>
       <c r="Q88" t="n">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="R88" t="n">
-        <v>716</v>
+        <v>335</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -8652,17 +8644,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>1204729944</t>
+          <t>1173391234</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1204729944</t>
+          <t>https://m.place.naver.com/place/1173391234</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8674,12 +8666,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JM NAIL</t>
+          <t>핑크네일</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>qkrwjddms105@naver.com</t>
+          <t>kwy765300@naver.com</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -8687,12 +8679,12 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 258 연산해수피아 2층</t>
+          <t>부산광역시 연제구 쌍미천로 120 핑크네일</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jmnail0104</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -8702,7 +8694,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -8723,17 +8715,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q89" t="n">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="R89" t="n">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -8742,17 +8734,17 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>1875116182</t>
+          <t>1040392199</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1875116182</t>
+          <t>https://m.place.naver.com/place/1040392199</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8764,29 +8756,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>꼼네일</t>
+          <t>썸네일</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>immire@naver.com</t>
+          <t>taiji0929@naver.com</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0507-1319-4713</t>
+          <t>051-852-4153</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 법원북로 13 쌍용스윗닷홈 상가 105호</t>
+          <t>부산광역시 연제구 고분로 16 썸네일</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>http://instagram.com/nail_ggom</t>
+          <t>https://www.instagram.com/taiji0929</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -8812,7 +8804,7 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8821,13 +8813,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="Q90" t="n">
-        <v>15</v>
+        <v>274</v>
       </c>
       <c r="R90" t="n">
-        <v>48</v>
+        <v>317</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8836,17 +8828,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>1200894164</t>
+          <t>35243970</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1200894164</t>
+          <t>https://m.place.naver.com/place/35243970</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8858,29 +8850,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>올바른 네일&amp;브로우</t>
+          <t>히니네일 부산연산점</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>stylemusee@naver.com</t>
+          <t>yuu_ja@naver.com</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0507-1416-7885</t>
+          <t>0507-1391-1454</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 82 205호</t>
+          <t>부산광역시 연제구 중앙대로 1130 연산동 SK VIE W 2단지 1층 114호</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ab_browlab</t>
+          <t>https://www.instagram.com/heeni_nail</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -8915,13 +8907,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="Q91" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="R91" t="n">
-        <v>213</v>
+        <v>137</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -8930,17 +8922,17 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>1021114766</t>
+          <t>1114751434</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1021114766</t>
+          <t>https://m.place.naver.com/place/1114751434</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -8952,29 +8944,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>네일오예</t>
+          <t>모모네일</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>efjekkk0888@naver.com</t>
+          <t>brenda70@naver.com</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>0507-1424-0360</t>
+          <t>0507-1334-5238</t>
         </is>
       </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 해맞이로67번길 23 102호</t>
+          <t>부산광역시 연제구 명륜로2번길 32 3층 모모네일</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_o.yeah?igsh=MTBrcDN2OHM5djY1cQ%3D%3D&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -8984,7 +8976,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -9005,17 +8997,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -9024,17 +9016,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>2070499527</t>
+          <t>1664773879</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2070499527</t>
+          <t>https://m.place.naver.com/place/1664773879</t>
         </is>
       </c>
       <c r="V92" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9046,29 +9038,25 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>에스네일</t>
+          <t>화양연화</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>7gonggu@naver.com</t>
+          <t>k0110ksc@naver.com</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>0507-1303-4143</t>
-        </is>
-      </c>
+      <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 258 연산해수피아 1층 105호</t>
+          <t>부산광역시 연제구 연안로13번길 53 1층</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/7gonggu</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -9078,12 +9066,12 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -9099,17 +9087,17 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="Q93" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -9118,17 +9106,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>1772096643</t>
+          <t>1137724225</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1772096643</t>
+          <t>https://m.place.naver.com/place/1137724225</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9140,29 +9128,29 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>모어브 네일스튜디오</t>
+          <t>꼼네일</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>pilates_youl@naver.com</t>
+          <t>immire@naver.com</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>0507-1382-2699</t>
+          <t>0507-1319-4713</t>
         </is>
       </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1038번길 40 행복주택2단지 근린생활시설D동 201호</t>
+          <t>부산광역시 연제구 법원북로 13 쌍용스윗닷홈 상가 105호</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/moav_nail</t>
+          <t>http://instagram.com/nail_ggom</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -9188,7 +9176,7 @@
       <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9197,13 +9185,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="Q94" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="R94" t="n">
-        <v>158</v>
+        <v>48</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -9212,17 +9200,17 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>1806276546</t>
+          <t>1200894164</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1806276546</t>
+          <t>https://m.place.naver.com/place/1200894164</t>
         </is>
       </c>
       <c r="V94" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9234,25 +9222,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>츄제이네일 부산연산점</t>
+          <t>수네일아트</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>qhdwkzz@naver.com</t>
+          <t>very_cake@naver.com</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>0507-1400-4149</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1130 SK뷰 2단지 2층 216호 츄제이네일</t>
+          <t>부산광역시 연제구 명륜로2번길 7 삼익퓨처타워상가 101동 3층 311호 수네일아트</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chuuj_nail</t>
+          <t>https://youtube.com/</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -9283,17 +9275,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>225</v>
+        <v>6</v>
       </c>
       <c r="Q95" t="n">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>333</v>
+        <v>7</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -9302,17 +9294,17 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>1173391234</t>
+          <t>12869643</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1173391234</t>
+          <t>https://m.place.naver.com/place/12869643</t>
         </is>
       </c>
       <c r="V95" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9324,29 +9316,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>네일노마 연산역점</t>
+          <t>네일시스</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>mison0327@naver.com</t>
+          <t>mjmj012@naver.com</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>0507-1320-0958</t>
+          <t>0507-1409-0104</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로91번길 20 유림스카이 1층 101호</t>
+          <t>부산광역시 연제구 거제천로124번길 48 1층 101호</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailnoma</t>
+          <t>https://www.instagram.com/__nailsis</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -9381,13 +9373,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>371</v>
+        <v>34</v>
       </c>
       <c r="Q96" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>404</v>
+        <v>34</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -9396,17 +9388,17 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>1708779082</t>
+          <t>1498091323</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1708779082</t>
+          <t>https://m.place.naver.com/place/1498091323</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9418,29 +9410,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>네일 더 드리밍 연산시청점</t>
+          <t>코코네일</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ssongs_yummy@naver.com</t>
+          <t>jjuahlee@naver.com</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0507-1347-4595</t>
+          <t>0507-1305-1030</t>
         </is>
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로 8 1층 네일 더 드리밍 연산시청점</t>
+          <t>부산광역시 연제구 쌍미천로151번길 17</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_the.dreaming</t>
+          <t>http://instagram.com/coconail_mj</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -9475,13 +9467,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>236</v>
+        <v>8</v>
       </c>
       <c r="Q97" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="R97" t="n">
-        <v>254</v>
+        <v>10</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -9490,17 +9482,17 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>1491294937</t>
+          <t>1043623932</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1491294937</t>
+          <t>https://m.place.naver.com/place/1043623932</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9512,29 +9504,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>어썸네일</t>
+          <t>여우네일</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>loves0226@naver.com</t>
+          <t>assajuju1104@naver.com</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>0507-1366-2967</t>
-        </is>
-      </c>
+      <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 안연로 24 1층</t>
+          <t>부산광역시 연제구 아시아드대로 82 2층</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/awesome_nail_2967</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -9544,7 +9532,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -9565,17 +9553,17 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="Q98" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -9584,17 +9572,17 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>1637674026</t>
+          <t>19997542</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1637674026</t>
+          <t>https://m.place.naver.com/place/19997542</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9606,29 +9594,29 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>네일이냥</t>
+          <t>다유네일</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>nail-nyang@naver.com</t>
+          <t>djbigbang@naver.com</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>051-867-4377</t>
+          <t>0507-1415-0598</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로294번길 10 네일이냥 (동원베네스트, 상가)</t>
+          <t>부산광역시 연제구 아시아드대로 39 레이카운티 2단지상가 207호</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/nail-nyang</t>
+          <t>https://www.instagram.com/dayoonail</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -9643,7 +9631,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -9663,13 +9651,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>37</v>
+        <v>2244</v>
       </c>
       <c r="Q99" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R99" t="n">
-        <v>38</v>
+        <v>2258</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -9678,17 +9666,17 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>1081723048</t>
+          <t>1387061591</t>
         </is>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1081723048</t>
+          <t>https://m.place.naver.com/place/1387061591</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9700,34 +9688,34 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>소르베네일 부산시청점</t>
+          <t>라온네일</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>oladeoro@naver.com</t>
+          <t>sungunara226@naver.com</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0507-1487-4679</t>
+          <t>0507-1364-1656</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1038번길 40 근린생활시설 D동 2층 208호</t>
+          <t>부산광역시 연제구 고분로32번길 23 1층</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xdHhHn</t>
+          <t>http://instagram.com/la_on_nail</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -9748,7 +9736,7 @@
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
@@ -9757,13 +9745,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="Q100" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="R100" t="n">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -9772,17 +9760,17 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>2032602450</t>
+          <t>1100502822</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2032602450</t>
+          <t>https://m.place.naver.com/place/1100502822</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9794,29 +9782,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>뷰티더무드네일</t>
+          <t>꼭대기네일</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>cjsdkwls12@naver.com</t>
+          <t>foresten@naver.com</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0507-1438-2849</t>
+          <t>0507-1340-4140</t>
         </is>
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로1043번길 12 2층</t>
+          <t>부산광역시 연제구 화지로 95 거제청구하이츠아파트 상가동 1층</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sgAjvNkg</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -9826,7 +9814,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -9842,22 +9830,22 @@
       <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P101" t="n">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="Q101" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>147</v>
+        <v>22</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -9866,17 +9854,17 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>1636008279</t>
+          <t>1056754569</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1636008279</t>
+          <t>https://m.place.naver.com/place/1056754569</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9888,29 +9876,29 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>네시일분 예뻐지는시간</t>
+          <t>채움네일</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>alal7667@naver.com</t>
+          <t>rhdwnsla5656@naver.com</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0507-1335-9404</t>
+          <t>0507-1340-9768</t>
         </is>
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로343번길 22 더스타a동 101호 네시일분</t>
+          <t>부산광역시 연제구 월드컵대로 7 2층</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nesiilbun_beauty</t>
+          <t>https://www.instagram.com/yoming22</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -9945,13 +9933,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="Q102" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="R102" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -9960,17 +9948,17 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>1660019694</t>
+          <t>1801826590</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1660019694</t>
+          <t>https://m.place.naver.com/place/1801826590</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -9982,34 +9970,34 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>리앤뷰티네일</t>
+          <t>올바른 네일&amp;브로우</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>wnqkf517@naver.com</t>
+          <t>stylemusee@naver.com</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>0507-1341-3798</t>
+          <t>0507-1416-7885</t>
         </is>
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로 105-1 3층 리앤뷰티네일</t>
+          <t>부산광역시 연제구 거제천로 82 205호</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/</t>
+          <t>https://www.instagram.com/ab_browlab</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10019,7 +10007,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10039,13 +10027,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>10</v>
+        <v>173</v>
       </c>
       <c r="Q103" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="R103" t="n">
-        <v>11</v>
+        <v>213</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -10054,17 +10042,17 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>1056219004</t>
+          <t>1021114766</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1056219004</t>
+          <t>https://m.place.naver.com/place/1021114766</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10076,29 +10064,29 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>다유네일</t>
+          <t>패디당</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>djbigbang@naver.com</t>
+          <t>pedidang@naver.com</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>0507-1415-0598</t>
+          <t>0507-1302-3954</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로 39 레이카운티 2단지상가 207호</t>
+          <t>부산광역시 연제구 거제천로 82 삼정그린코아 포레스트 상가동 2층 211호</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dayoonail</t>
+          <t>https://www.instagram.com/pedi._.dang</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -10133,13 +10121,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2238</v>
+        <v>12</v>
       </c>
       <c r="Q104" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2252</v>
+        <v>12</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -10148,17 +10136,17 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>1387061591</t>
+          <t>2026492166</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1387061591</t>
+          <t>https://m.place.naver.com/place/2026492166</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10170,29 +10158,29 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>네일한날</t>
+          <t>명월네일샵</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ch5502@naver.com</t>
+          <t>leekatanail@naver.com</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>0507-1402-2670</t>
+          <t>0507-1461-1196</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 80 107동 112호</t>
+          <t>부산광역시 연제구 거제천로 246</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailhannal2670</t>
+          <t>https://blog.naver.com/leekatanail</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -10207,7 +10195,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10227,13 +10215,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>255</v>
+        <v>40</v>
       </c>
       <c r="Q105" t="n">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="R105" t="n">
-        <v>309</v>
+        <v>50</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -10242,17 +10230,17 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>1298434527</t>
+          <t>1031904006</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1298434527</t>
+          <t>https://m.place.naver.com/place/1031904006</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10264,29 +10252,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>바나다네일</t>
+          <t>엔피케어 부산연산점</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>ksn0706@naver.com</t>
+          <t>np_care@naver.com</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>0507-1332-8909</t>
+          <t>0507-1449-2096</t>
         </is>
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 쌍미천로 163-1 바나다네일</t>
+          <t>부산광역시 연제구 중앙대로 1114 4층</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ksn0706</t>
+          <t>https://www.youtube.com/@NPCARE_</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -10321,13 +10309,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>129</v>
+        <v>579</v>
       </c>
       <c r="Q106" t="n">
-        <v>33</v>
+        <v>137</v>
       </c>
       <c r="R106" t="n">
-        <v>162</v>
+        <v>716</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
@@ -10336,17 +10324,17 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>34818659</t>
+          <t>1204729944</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/34818659</t>
+          <t>https://m.place.naver.com/place/1204729944</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10358,29 +10346,29 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2월11일네일</t>
+          <t>어썸네일</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>211nail_0211@naver.com</t>
+          <t>loves0226@naver.com</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>0507-1329-6882</t>
+          <t>0507-1366-2967</t>
         </is>
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1063 5층</t>
+          <t>부산광역시 연제구 안연로 24 1층</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/211_nail</t>
+          <t>https://www.instagram.com/awesome_nail_2967</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -10415,13 +10403,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="Q107" t="n">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="R107" t="n">
-        <v>269</v>
+        <v>103</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -10430,17 +10418,17 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>1816506274</t>
+          <t>1637674026</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1816506274</t>
+          <t>https://m.place.naver.com/place/1637674026</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10452,29 +10440,29 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>네일르엔</t>
+          <t>바나다네일</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>reruns_@naver.com</t>
+          <t>ksn0706@naver.com</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>0507-1357-6422</t>
+          <t>0507-1332-8909</t>
         </is>
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로 140 상진빌딩 2층</t>
+          <t>부산광역시 연제구 쌍미천로 163-1 바나다네일</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_le.n</t>
+          <t>https://blog.naver.com/ksn0706</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -10489,7 +10477,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -10500,7 +10488,7 @@
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O108" t="inlineStr">
@@ -10509,13 +10497,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="Q108" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="R108" t="n">
-        <v>205</v>
+        <v>162</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -10524,17 +10512,17 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>1665472449</t>
+          <t>34818659</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1665472449</t>
+          <t>https://m.place.naver.com/place/34818659</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10546,29 +10534,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>더미뉴네일</t>
+          <t>오늘의네일</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>mj_2023@naver.com</t>
+          <t>redcherry88@naver.com</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>0507-1460-0699</t>
+          <t>0507-1398-3444</t>
         </is>
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연수로 173 1층</t>
+          <t>부산광역시 연제구 고분로 254 1층</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/theminew.nail</t>
+          <t>http://instagram.com/cny3444</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -10603,13 +10591,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>130</v>
+        <v>5</v>
       </c>
       <c r="Q109" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="R109" t="n">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
@@ -10618,17 +10606,17 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>1260374485</t>
+          <t>1838257805</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1260374485</t>
+          <t>https://m.place.naver.com/place/1838257805</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10640,29 +10628,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>네일그리다</t>
+          <t>네일노마 연산역점</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>duz8107@naver.com</t>
+          <t>mison0327@naver.com</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>0507-1321-5388</t>
+          <t>0507-1320-0958</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 반송로 68 네일그리다</t>
+          <t>부산광역시 연제구 월드컵대로91번길 20 유림스카이 1층 101호</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nailgrida_jh</t>
+          <t>https://www.instagram.com/nailnoma</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -10697,13 +10685,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>229</v>
+        <v>371</v>
       </c>
       <c r="Q110" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="R110" t="n">
-        <v>289</v>
+        <v>404</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -10712,17 +10700,17 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>38404003</t>
+          <t>1708779082</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38404003</t>
+          <t>https://m.place.naver.com/place/1708779082</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10734,34 +10722,34 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>네일리크</t>
+          <t>신지네일&amp;메이크업 연산동점</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>nailique25@naver.com</t>
+          <t>springonion_eggs@naver.com</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>0507-1449-2433</t>
+          <t>0507-1309-9627</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 월드컵대로79번길 50 1층</t>
+          <t>부산광역시 연제구 중앙대로1124번길 15 1층상가</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_Vyesn</t>
+          <t>https://www.instagram.com/shinzinail/</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -10782,7 +10770,7 @@
       <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -10791,13 +10779,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>316</v>
+        <v>181</v>
       </c>
       <c r="Q111" t="n">
-        <v>29</v>
+        <v>294</v>
       </c>
       <c r="R111" t="n">
-        <v>345</v>
+        <v>475</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -10806,17 +10794,17 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>1290184827</t>
+          <t>1776187392</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1290184827</t>
+          <t>https://m.place.naver.com/place/1776187392</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10828,29 +10816,29 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>프롬제이네일</t>
+          <t>보니또네일</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>fromjnail-@naver.com</t>
+          <t>ourcutelove@naver.com</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>0507-1464-0002</t>
+          <t>0507-1479-7034</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 법원북로41번길 5 거제동원로얄듀크3차 상가동 B1층</t>
+          <t>부산광역시 연제구 고분로 200 상가동 107호</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fromjnail-</t>
+          <t>https://www.instagram.com/bonitto__nail</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -10865,7 +10853,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -10885,13 +10873,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="Q112" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="R112" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -10900,17 +10888,17 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>2029616168</t>
+          <t>1222997854</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029616168</t>
+          <t>https://m.place.naver.com/place/1222997854</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -10922,25 +10910,29 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>화양연화</t>
+          <t>리본네일 부산시청점</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>glory4u_lee@naver.com</t>
+          <t>girljakpoom@naver.com</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0507-1442-5066</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 연안로13번길 53 1층</t>
+          <t>부산광역시 연제구 중앙대로1043번길 56 2층 리본네일 부산시청점</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/girljakpoom</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -10950,12 +10942,12 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -10971,17 +10963,17 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>25</v>
+        <v>142</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R113" t="n">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -10990,17 +10982,17 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>1137724225</t>
+          <t>1260057809</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1137724225</t>
+          <t>https://m.place.naver.com/place/1260057809</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11012,29 +11004,29 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>이퓨리네일 연산점</t>
+          <t>레푸스 연산시청점</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ifurynail@naver.com</t>
+          <t>refuss_@naver.com</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>0507-1356-4466</t>
+          <t>0507-1443-6687</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 거제천로230번길 81 유성헤네스타워 상가 1층 이퓨리네일</t>
+          <t>부산광역시 연제구 시청로 26-1 2층 (베스킨라빈스건물)</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ifurynail</t>
+          <t>https://www.instagram.com/refuss_yeonsan</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -11049,7 +11041,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -11069,13 +11061,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>249</v>
+        <v>1482</v>
       </c>
       <c r="Q114" t="n">
-        <v>35</v>
+        <v>432</v>
       </c>
       <c r="R114" t="n">
-        <v>284</v>
+        <v>1914</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -11084,17 +11076,17 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>1044877447</t>
+          <t>1842243644</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044877447</t>
+          <t>https://m.place.naver.com/place/1842243644</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11106,29 +11098,29 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>수네일아트</t>
+          <t>제이제이네일&amp;붙임머리 거제사직점</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>very_cake@naver.com</t>
+          <t>kiss121127@naver.com</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>0507-1400-4149</t>
+          <t>0507-1335-5968</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 명륜로2번길 7 삼익퓨처타워상가 101동 3층 311호 수네일아트</t>
+          <t>부산광역시 연제구 아시아드대로 39 레이카운티 1단지상가 109호</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://youtube.com/</t>
+          <t>https://www.instagram.com/jj__nail</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -11159,17 +11151,17 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>6</v>
+        <v>384</v>
       </c>
       <c r="Q115" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="R115" t="n">
-        <v>7</v>
+        <v>418</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -11178,17 +11170,17 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>12869643</t>
+          <t>1823710447</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12869643</t>
+          <t>https://m.place.naver.com/place/1823710447</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11200,29 +11192,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>네일이나</t>
+          <t>네일한날</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>merryhunter@naver.com</t>
+          <t>vicki79@naver.com</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>0507-1323-8536</t>
+          <t>0507-1402-2670</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로 17-1 1층</t>
+          <t>부산광역시 연제구 반송로 80 107동 112호</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/nailhannal2670</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -11232,7 +11224,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -11257,13 +11249,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>9</v>
+        <v>256</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="R116" t="n">
-        <v>9</v>
+        <v>310</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -11272,17 +11264,17 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>2043892240</t>
+          <t>1298434527</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2043892240</t>
+          <t>https://m.place.naver.com/place/1298434527</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11294,29 +11286,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>네일,별</t>
+          <t>루미가넷 네일존 사직</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>nagi96@naver.com</t>
+          <t>webmore@naver.com</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>0507-1379-2261</t>
+          <t>070-7012-9336</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙천로19번길 46 2층</t>
+          <t>부산광역시 연제구 종합운동장로 7 아시아드 홈플러스 지하1층 네일존</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nail_byeol_</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -11326,7 +11318,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -11347,17 +11339,17 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>92</v>
+        <v>3</v>
       </c>
       <c r="Q117" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -11366,17 +11358,17 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>1252164677</t>
+          <t>1179495995</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1252164677</t>
+          <t>https://m.place.naver.com/place/1179495995</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11388,29 +11380,29 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>라로제네일</t>
+          <t>랑뷰티</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>brushlounge@naver.com</t>
+          <t>loving0258@naver.com</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>0507-1343-8177</t>
+          <t>0507-1490-3542</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 신금로 18 2층</t>
+          <t>부산광역시 연제구 거제천로255번길 48 1층</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sYvUmDpi</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -11420,7 +11412,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -11436,7 +11428,7 @@
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -11445,13 +11437,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
         <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -11460,17 +11452,17 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>2039316974</t>
+          <t>2088276975</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2039316974</t>
+          <t>https://m.place.naver.com/place/2088276975</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11482,25 +11474,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>챠밍네일 연산점</t>
+          <t>이퓨리네일 연산점</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ghdrldbwjd1@naver.com</t>
+          <t>ifurynail@naver.com</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>0507-1356-4466</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 과정로260번길 32 챠밍네일</t>
+          <t>부산광역시 연제구 거제천로230번길 81 유성헤네스타워 상가 1층 이퓨리네일</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ghdrldbwjd1</t>
+          <t>https://blog.naver.com/ifurynail</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -11535,13 +11531,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>132</v>
+        <v>249</v>
       </c>
       <c r="Q119" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="R119" t="n">
-        <v>151</v>
+        <v>284</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -11550,17 +11546,17 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>1458074178</t>
+          <t>1044877447</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1458074178</t>
+          <t>https://m.place.naver.com/place/1044877447</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11572,29 +11568,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ONE네일</t>
+          <t>가온네일</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>garam_soo@naver.com</t>
+          <t>leedmswh8898@naver.com</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>0507-1349-6159</t>
+          <t>0507-1345-8019</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 중앙대로 1049 3층</t>
+          <t>부산광역시 연제구 거제천로 82 삼정그린코아포레스트 상가동 210호</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://instagram.com/onenail_onenail?igshid=ZDdkNTZiNTM=</t>
+          <t>https://www.instagram.com/gaonnail_/</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -11629,13 +11625,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="Q120" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="R120" t="n">
-        <v>103</v>
+        <v>263</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -11644,17 +11640,17 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>1153323846</t>
+          <t>1960748053</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153323846</t>
+          <t>https://m.place.naver.com/place/1960748053</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -11666,29 +11662,29 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>제이제이네일&amp;붙임머리 거제사직점</t>
+          <t>유니스네일뷰티</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>kiss121127@naver.com</t>
+          <t>soyun4241@naver.com</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>0507-1335-5968</t>
+          <t>0507-1382-4241</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>부산광역시 연제구 아시아드대로 39 레이카운티 1단지상가 109호</t>
+          <t>부산광역시 연제구 거제천로230번길 61 1층 유니스네일뷰티</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jj__nail</t>
+          <t>https://www.instagram.com/artist_yunice</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -11723,32 +11719,310 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>384</v>
+        <v>136</v>
       </c>
       <c r="Q121" t="n">
+        <v>31</v>
+      </c>
+      <c r="R121" t="n">
+        <v>167</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>1725318910</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1725318910</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>바이요니네일</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>kitty_log@naver.com</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>부산광역시 연제구 중앙천로 77-2 1층</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>http://instagram.com/byyoni__nail</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P122" t="n">
+        <v>463</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>7</v>
+      </c>
+      <c r="R122" t="n">
+        <v>470</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>1418772825</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1418772825</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>네일존 이마트연제점</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>nailzone__@naver.com</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>0507-1448-9396</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>부산광역시 연제구 연수로 89 이마트 연제점 3층</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/nailzone__</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P123" t="n">
+        <v>221</v>
+      </c>
+      <c r="Q123" t="n">
         <v>34</v>
       </c>
-      <c r="R121" t="n">
-        <v>418</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T121" t="inlineStr">
-        <is>
-          <t>1823710447</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1823710447</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>2026-04-28</t>
+      <c r="R123" t="n">
+        <v>255</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>1531070526</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1531070526</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>네일아트,네일샵</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>프롬제이네일</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>fromjnail-@naver.com</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>0507-1464-0002</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>부산광역시 연제구 법원북로41번길 5 거제동원로얄듀크3차 상가동 B1층</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fromjnail-</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P124" t="n">
+        <v>106</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>14</v>
+      </c>
+      <c r="R124" t="n">
+        <v>120</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>2029616168</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2029616168</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
